--- a/output/version3/test/20-10/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>877</v>
+        <v>927</v>
       </c>
       <c r="C2" t="n">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="D2" t="n">
-        <v>781</v>
+        <v>970</v>
       </c>
       <c r="E2" t="n">
-        <v>1034</v>
+        <v>921</v>
       </c>
       <c r="F2" t="n">
-        <v>921</v>
+        <v>885</v>
       </c>
       <c r="G2" t="n">
-        <v>890</v>
+        <v>820</v>
       </c>
       <c r="H2" t="n">
-        <v>850</v>
+        <v>931</v>
       </c>
       <c r="I2" t="n">
-        <v>894</v>
+        <v>919</v>
       </c>
       <c r="J2" t="n">
-        <v>1018</v>
+        <v>884</v>
       </c>
       <c r="K2" t="n">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="L2" t="n">
-        <v>892.3</v>
+        <v>887</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>796</v>
+        <v>744</v>
       </c>
       <c r="C3" t="n">
+        <v>784</v>
+      </c>
+      <c r="D3" t="n">
+        <v>962</v>
+      </c>
+      <c r="E3" t="n">
+        <v>878</v>
+      </c>
+      <c r="F3" t="n">
+        <v>918</v>
+      </c>
+      <c r="G3" t="n">
+        <v>981</v>
+      </c>
+      <c r="H3" t="n">
+        <v>913</v>
+      </c>
+      <c r="I3" t="n">
         <v>840</v>
       </c>
-      <c r="D3" t="n">
-        <v>904</v>
-      </c>
-      <c r="E3" t="n">
-        <v>922</v>
-      </c>
-      <c r="F3" t="n">
-        <v>740</v>
-      </c>
-      <c r="G3" t="n">
-        <v>969</v>
-      </c>
-      <c r="H3" t="n">
-        <v>861</v>
-      </c>
-      <c r="I3" t="n">
-        <v>963</v>
-      </c>
       <c r="J3" t="n">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="K3" t="n">
-        <v>832</v>
+        <v>942</v>
       </c>
       <c r="L3" t="n">
-        <v>869.8</v>
+        <v>883.5</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="C4" t="n">
-        <v>817</v>
+        <v>874</v>
       </c>
       <c r="D4" t="n">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="E4" t="n">
-        <v>830</v>
+        <v>875</v>
       </c>
       <c r="F4" t="n">
-        <v>769</v>
+        <v>807</v>
       </c>
       <c r="G4" t="n">
-        <v>701</v>
+        <v>880</v>
       </c>
       <c r="H4" t="n">
-        <v>891</v>
+        <v>805</v>
       </c>
       <c r="I4" t="n">
-        <v>888</v>
+        <v>989</v>
       </c>
       <c r="J4" t="n">
-        <v>914</v>
+        <v>846</v>
       </c>
       <c r="K4" t="n">
-        <v>839</v>
+        <v>777</v>
       </c>
       <c r="L4" t="n">
-        <v>838.1</v>
+        <v>861.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>916</v>
+        <v>857</v>
       </c>
       <c r="C5" t="n">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="D5" t="n">
-        <v>876</v>
+        <v>769</v>
       </c>
       <c r="E5" t="n">
-        <v>975</v>
+        <v>795</v>
       </c>
       <c r="F5" t="n">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="G5" t="n">
-        <v>782</v>
+        <v>821</v>
       </c>
       <c r="H5" t="n">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="I5" t="n">
-        <v>901</v>
+        <v>980</v>
       </c>
       <c r="J5" t="n">
-        <v>828</v>
+        <v>811</v>
       </c>
       <c r="K5" t="n">
-        <v>907</v>
+        <v>865</v>
       </c>
       <c r="L5" t="n">
-        <v>872.3</v>
+        <v>847.2</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>847</v>
+        <v>902</v>
       </c>
       <c r="C6" t="n">
-        <v>866</v>
+        <v>885</v>
       </c>
       <c r="D6" t="n">
-        <v>969</v>
+        <v>728</v>
       </c>
       <c r="E6" t="n">
-        <v>875</v>
+        <v>792</v>
       </c>
       <c r="F6" t="n">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="G6" t="n">
-        <v>839</v>
+        <v>916</v>
       </c>
       <c r="H6" t="n">
-        <v>773</v>
+        <v>713</v>
       </c>
       <c r="I6" t="n">
-        <v>799</v>
+        <v>896</v>
       </c>
       <c r="J6" t="n">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="K6" t="n">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="L6" t="n">
-        <v>840.7</v>
+        <v>825.8</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>853</v>
+        <v>833</v>
       </c>
       <c r="C7" t="n">
-        <v>843</v>
+        <v>904</v>
       </c>
       <c r="D7" t="n">
-        <v>769</v>
+        <v>812</v>
       </c>
       <c r="E7" t="n">
-        <v>816</v>
+        <v>838</v>
       </c>
       <c r="F7" t="n">
-        <v>789</v>
+        <v>901</v>
       </c>
       <c r="G7" t="n">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="H7" t="n">
-        <v>781</v>
+        <v>810</v>
       </c>
       <c r="I7" t="n">
-        <v>927</v>
+        <v>832</v>
       </c>
       <c r="J7" t="n">
-        <v>741</v>
+        <v>842</v>
       </c>
       <c r="K7" t="n">
-        <v>838</v>
+        <v>951</v>
       </c>
       <c r="L7" t="n">
-        <v>822.3</v>
+        <v>860.1</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>860</v>
+        <v>838</v>
       </c>
       <c r="C8" t="n">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="D8" t="n">
-        <v>735</v>
+        <v>817</v>
       </c>
       <c r="E8" t="n">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="F8" t="n">
-        <v>818</v>
+        <v>791</v>
       </c>
       <c r="G8" t="n">
-        <v>999</v>
+        <v>956</v>
       </c>
       <c r="H8" t="n">
-        <v>873</v>
+        <v>803</v>
       </c>
       <c r="I8" t="n">
-        <v>862</v>
+        <v>957</v>
       </c>
       <c r="J8" t="n">
-        <v>890</v>
+        <v>978</v>
       </c>
       <c r="K8" t="n">
-        <v>964</v>
+        <v>990</v>
       </c>
       <c r="L8" t="n">
-        <v>878.8</v>
+        <v>888.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>942</v>
+        <v>840</v>
       </c>
       <c r="C9" t="n">
-        <v>920</v>
+        <v>755</v>
       </c>
       <c r="D9" t="n">
-        <v>1013</v>
+        <v>965</v>
       </c>
       <c r="E9" t="n">
-        <v>765</v>
+        <v>911</v>
       </c>
       <c r="F9" t="n">
-        <v>1094</v>
+        <v>869</v>
       </c>
       <c r="G9" t="n">
-        <v>915</v>
+        <v>894</v>
       </c>
       <c r="H9" t="n">
-        <v>867</v>
+        <v>939</v>
       </c>
       <c r="I9" t="n">
-        <v>884</v>
+        <v>829</v>
       </c>
       <c r="J9" t="n">
-        <v>868</v>
+        <v>881</v>
       </c>
       <c r="K9" t="n">
-        <v>838</v>
+        <v>860</v>
       </c>
       <c r="L9" t="n">
-        <v>910.6</v>
+        <v>874.3</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>810</v>
+        <v>749</v>
       </c>
       <c r="C10" t="n">
-        <v>764</v>
+        <v>856</v>
       </c>
       <c r="D10" t="n">
-        <v>733</v>
+        <v>812</v>
       </c>
       <c r="E10" t="n">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="F10" t="n">
-        <v>764</v>
+        <v>690</v>
       </c>
       <c r="G10" t="n">
-        <v>816</v>
+        <v>829</v>
       </c>
       <c r="H10" t="n">
-        <v>731</v>
+        <v>757</v>
       </c>
       <c r="I10" t="n">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="J10" t="n">
+        <v>830</v>
+      </c>
+      <c r="K10" t="n">
         <v>789</v>
       </c>
-      <c r="K10" t="n">
-        <v>801</v>
-      </c>
       <c r="L10" t="n">
-        <v>783.7</v>
+        <v>791.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>795</v>
+        <v>770</v>
       </c>
       <c r="C11" t="n">
-        <v>810</v>
+        <v>961</v>
       </c>
       <c r="D11" t="n">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E11" t="n">
-        <v>914</v>
+        <v>727</v>
       </c>
       <c r="F11" t="n">
-        <v>706</v>
+        <v>793</v>
       </c>
       <c r="G11" t="n">
-        <v>914</v>
+        <v>787</v>
       </c>
       <c r="H11" t="n">
-        <v>819</v>
+        <v>856</v>
       </c>
       <c r="I11" t="n">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="J11" t="n">
-        <v>769</v>
+        <v>873</v>
       </c>
       <c r="K11" t="n">
-        <v>887</v>
+        <v>859</v>
       </c>
       <c r="L11" t="n">
-        <v>824.6</v>
+        <v>825.3</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>740</v>
+        <v>775</v>
       </c>
       <c r="C12" t="n">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="D12" t="n">
+        <v>843</v>
+      </c>
+      <c r="E12" t="n">
+        <v>890</v>
+      </c>
+      <c r="F12" t="n">
+        <v>842</v>
+      </c>
+      <c r="G12" t="n">
         <v>877</v>
       </c>
-      <c r="E12" t="n">
-        <v>918</v>
-      </c>
-      <c r="F12" t="n">
-        <v>846</v>
-      </c>
-      <c r="G12" t="n">
-        <v>770</v>
-      </c>
       <c r="H12" t="n">
-        <v>791</v>
+        <v>829</v>
       </c>
       <c r="I12" t="n">
-        <v>907</v>
+        <v>931</v>
       </c>
       <c r="J12" t="n">
-        <v>768</v>
+        <v>807</v>
       </c>
       <c r="K12" t="n">
-        <v>863</v>
+        <v>887</v>
       </c>
       <c r="L12" t="n">
-        <v>829.6</v>
+        <v>849.1</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>781</v>
+        <v>858</v>
       </c>
       <c r="C13" t="n">
-        <v>801</v>
+        <v>883</v>
       </c>
       <c r="D13" t="n">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>856</v>
       </c>
       <c r="F13" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="G13" t="n">
-        <v>785</v>
+        <v>867</v>
       </c>
       <c r="H13" t="n">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="I13" t="n">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="J13" t="n">
-        <v>940</v>
+        <v>721</v>
       </c>
       <c r="K13" t="n">
-        <v>1010</v>
+        <v>882</v>
       </c>
       <c r="L13" t="n">
-        <v>867</v>
+        <v>853.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>856</v>
+        <v>1007</v>
       </c>
       <c r="C14" t="n">
-        <v>771</v>
+        <v>875</v>
       </c>
       <c r="D14" t="n">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="E14" t="n">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="F14" t="n">
+        <v>873</v>
+      </c>
+      <c r="G14" t="n">
         <v>875</v>
       </c>
-      <c r="G14" t="n">
-        <v>970</v>
-      </c>
       <c r="H14" t="n">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="I14" t="n">
-        <v>949</v>
+        <v>838</v>
       </c>
       <c r="J14" t="n">
-        <v>832</v>
+        <v>932</v>
       </c>
       <c r="K14" t="n">
-        <v>949</v>
+        <v>969</v>
       </c>
       <c r="L14" t="n">
-        <v>885.6</v>
+        <v>902.2</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="C15" t="n">
-        <v>889</v>
+        <v>917</v>
       </c>
       <c r="D15" t="n">
-        <v>976</v>
+        <v>899</v>
       </c>
       <c r="E15" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="F15" t="n">
-        <v>817</v>
+        <v>836</v>
       </c>
       <c r="G15" t="n">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="H15" t="n">
-        <v>954</v>
+        <v>777</v>
       </c>
       <c r="I15" t="n">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="J15" t="n">
-        <v>913</v>
+        <v>946</v>
       </c>
       <c r="K15" t="n">
-        <v>856</v>
+        <v>845</v>
       </c>
       <c r="L15" t="n">
-        <v>884.7</v>
+        <v>870.2</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C16" t="n">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="D16" t="n">
-        <v>998</v>
+        <v>884</v>
       </c>
       <c r="E16" t="n">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="F16" t="n">
-        <v>927</v>
+        <v>869</v>
       </c>
       <c r="G16" t="n">
-        <v>909</v>
+        <v>849</v>
       </c>
       <c r="H16" t="n">
-        <v>852</v>
+        <v>775</v>
       </c>
       <c r="I16" t="n">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="J16" t="n">
-        <v>942</v>
+        <v>851</v>
       </c>
       <c r="K16" t="n">
-        <v>829</v>
+        <v>890</v>
       </c>
       <c r="L16" t="n">
-        <v>874</v>
+        <v>847.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>823</v>
+        <v>703</v>
       </c>
       <c r="C17" t="n">
-        <v>753</v>
+        <v>699</v>
       </c>
       <c r="D17" t="n">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="E17" t="n">
-        <v>802</v>
+        <v>872</v>
       </c>
       <c r="F17" t="n">
-        <v>761</v>
+        <v>830</v>
       </c>
       <c r="G17" t="n">
-        <v>778</v>
+        <v>739</v>
       </c>
       <c r="H17" t="n">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="I17" t="n">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="J17" t="n">
-        <v>766</v>
+        <v>864</v>
       </c>
       <c r="K17" t="n">
-        <v>864</v>
+        <v>804</v>
       </c>
       <c r="L17" t="n">
-        <v>797</v>
+        <v>790.9</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>961</v>
+        <v>993</v>
       </c>
       <c r="C18" t="n">
-        <v>922</v>
+        <v>988</v>
       </c>
       <c r="D18" t="n">
-        <v>797</v>
+        <v>940</v>
       </c>
       <c r="E18" t="n">
-        <v>1006</v>
+        <v>971</v>
       </c>
       <c r="F18" t="n">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="G18" t="n">
-        <v>936</v>
+        <v>952</v>
       </c>
       <c r="H18" t="n">
-        <v>998</v>
+        <v>916</v>
       </c>
       <c r="I18" t="n">
-        <v>934</v>
+        <v>913</v>
       </c>
       <c r="J18" t="n">
-        <v>944</v>
+        <v>802</v>
       </c>
       <c r="K18" t="n">
-        <v>918</v>
+        <v>878</v>
       </c>
       <c r="L18" t="n">
-        <v>929.6</v>
+        <v>925.3</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="C19" t="n">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="D19" t="n">
-        <v>728</v>
+        <v>780</v>
       </c>
       <c r="E19" t="n">
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="F19" t="n">
-        <v>705</v>
+        <v>773</v>
       </c>
       <c r="G19" t="n">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="H19" t="n">
-        <v>852</v>
+        <v>804</v>
       </c>
       <c r="I19" t="n">
-        <v>927</v>
+        <v>840</v>
       </c>
       <c r="J19" t="n">
-        <v>732</v>
+        <v>794</v>
       </c>
       <c r="K19" t="n">
-        <v>739</v>
+        <v>870</v>
       </c>
       <c r="L19" t="n">
-        <v>777</v>
+        <v>795.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>793</v>
+        <v>817</v>
       </c>
       <c r="C20" t="n">
-        <v>695</v>
+        <v>893</v>
       </c>
       <c r="D20" t="n">
-        <v>757</v>
+        <v>816</v>
       </c>
       <c r="E20" t="n">
-        <v>825</v>
+        <v>707</v>
       </c>
       <c r="F20" t="n">
-        <v>832</v>
+        <v>745</v>
       </c>
       <c r="G20" t="n">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="H20" t="n">
+        <v>817</v>
+      </c>
+      <c r="I20" t="n">
+        <v>781</v>
+      </c>
+      <c r="J20" t="n">
         <v>770</v>
       </c>
-      <c r="I20" t="n">
-        <v>736</v>
-      </c>
-      <c r="J20" t="n">
-        <v>729</v>
-      </c>
       <c r="K20" t="n">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="L20" t="n">
-        <v>771.2</v>
+        <v>794.4</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>751</v>
+        <v>922</v>
       </c>
       <c r="C21" t="n">
-        <v>830</v>
+        <v>783</v>
       </c>
       <c r="D21" t="n">
-        <v>978</v>
+        <v>928</v>
       </c>
       <c r="E21" t="n">
-        <v>807</v>
+        <v>1012</v>
       </c>
       <c r="F21" t="n">
-        <v>858</v>
+        <v>871</v>
       </c>
       <c r="G21" t="n">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="H21" t="n">
-        <v>826</v>
+        <v>923</v>
       </c>
       <c r="I21" t="n">
-        <v>1086</v>
+        <v>834</v>
       </c>
       <c r="J21" t="n">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="K21" t="n">
-        <v>912</v>
+        <v>891</v>
       </c>
       <c r="L21" t="n">
-        <v>870</v>
+        <v>883.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>862</v>
+        <v>908</v>
       </c>
       <c r="C22" t="n">
-        <v>930</v>
+        <v>872</v>
       </c>
       <c r="D22" t="n">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="E22" t="n">
-        <v>776</v>
+        <v>924</v>
       </c>
       <c r="F22" t="n">
-        <v>926</v>
+        <v>970</v>
       </c>
       <c r="G22" t="n">
-        <v>993</v>
+        <v>829</v>
       </c>
       <c r="H22" t="n">
-        <v>881</v>
+        <v>793</v>
       </c>
       <c r="I22" t="n">
-        <v>944</v>
+        <v>911</v>
       </c>
       <c r="J22" t="n">
-        <v>855</v>
+        <v>924</v>
       </c>
       <c r="K22" t="n">
-        <v>776</v>
+        <v>1074</v>
       </c>
       <c r="L22" t="n">
-        <v>878.5</v>
+        <v>903.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C23" t="n">
-        <v>1078</v>
+        <v>942</v>
       </c>
       <c r="D23" t="n">
-        <v>903</v>
+        <v>826</v>
       </c>
       <c r="E23" t="n">
-        <v>878</v>
+        <v>731</v>
       </c>
       <c r="F23" t="n">
-        <v>853</v>
+        <v>1002</v>
       </c>
       <c r="G23" t="n">
-        <v>833</v>
+        <v>766</v>
       </c>
       <c r="H23" t="n">
-        <v>793</v>
+        <v>993</v>
       </c>
       <c r="I23" t="n">
-        <v>818</v>
+        <v>904</v>
       </c>
       <c r="J23" t="n">
-        <v>809</v>
+        <v>850</v>
       </c>
       <c r="K23" t="n">
-        <v>788</v>
+        <v>869</v>
       </c>
       <c r="L23" t="n">
-        <v>868.4</v>
+        <v>881.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>961</v>
+        <v>941</v>
       </c>
       <c r="C24" t="n">
-        <v>738</v>
+        <v>787</v>
       </c>
       <c r="D24" t="n">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E24" t="n">
-        <v>973</v>
+        <v>848</v>
       </c>
       <c r="F24" t="n">
-        <v>829</v>
+        <v>883</v>
       </c>
       <c r="G24" t="n">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="H24" t="n">
-        <v>686</v>
+        <v>864</v>
       </c>
       <c r="I24" t="n">
-        <v>715</v>
+        <v>902</v>
       </c>
       <c r="J24" t="n">
-        <v>824</v>
+        <v>714</v>
       </c>
       <c r="K24" t="n">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="L24" t="n">
-        <v>823.8</v>
+        <v>845.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>873</v>
+        <v>812</v>
       </c>
       <c r="C25" t="n">
-        <v>896</v>
+        <v>816</v>
       </c>
       <c r="D25" t="n">
-        <v>800</v>
+        <v>970</v>
       </c>
       <c r="E25" t="n">
-        <v>816</v>
+        <v>856</v>
       </c>
       <c r="F25" t="n">
-        <v>892</v>
+        <v>846</v>
       </c>
       <c r="G25" t="n">
-        <v>821</v>
+        <v>853</v>
       </c>
       <c r="H25" t="n">
-        <v>862</v>
+        <v>823</v>
       </c>
       <c r="I25" t="n">
-        <v>884</v>
+        <v>846</v>
       </c>
       <c r="J25" t="n">
-        <v>959</v>
+        <v>888</v>
       </c>
       <c r="K25" t="n">
-        <v>858</v>
+        <v>901</v>
       </c>
       <c r="L25" t="n">
-        <v>866.1</v>
+        <v>861.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>875</v>
+        <v>920</v>
       </c>
       <c r="C26" t="n">
-        <v>1023</v>
+        <v>874</v>
       </c>
       <c r="D26" t="n">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="E26" t="n">
-        <v>878</v>
+        <v>939</v>
       </c>
       <c r="F26" t="n">
-        <v>882</v>
+        <v>933</v>
       </c>
       <c r="G26" t="n">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="H26" t="n">
-        <v>906</v>
+        <v>879</v>
       </c>
       <c r="I26" t="n">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="J26" t="n">
-        <v>856</v>
+        <v>937</v>
       </c>
       <c r="K26" t="n">
         <v>896</v>
       </c>
       <c r="L26" t="n">
-        <v>906.5</v>
+        <v>909.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="C27" t="n">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="D27" t="n">
-        <v>886</v>
+        <v>838</v>
       </c>
       <c r="E27" t="n">
-        <v>903</v>
+        <v>970</v>
       </c>
       <c r="F27" t="n">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="G27" t="n">
-        <v>886</v>
+        <v>957</v>
       </c>
       <c r="H27" t="n">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="I27" t="n">
-        <v>1054</v>
+        <v>986</v>
       </c>
       <c r="J27" t="n">
-        <v>968</v>
+        <v>867</v>
       </c>
       <c r="K27" t="n">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="L27" t="n">
-        <v>916.5</v>
+        <v>909</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>746</v>
+        <v>867</v>
       </c>
       <c r="C28" t="n">
-        <v>691</v>
+        <v>852</v>
       </c>
       <c r="D28" t="n">
-        <v>812</v>
+        <v>727</v>
       </c>
       <c r="E28" t="n">
-        <v>734</v>
+        <v>817</v>
       </c>
       <c r="F28" t="n">
-        <v>800</v>
+        <v>702</v>
       </c>
       <c r="G28" t="n">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="H28" t="n">
-        <v>818</v>
+        <v>780</v>
       </c>
       <c r="I28" t="n">
-        <v>902</v>
+        <v>861</v>
       </c>
       <c r="J28" t="n">
-        <v>831</v>
+        <v>884</v>
       </c>
       <c r="K28" t="n">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="L28" t="n">
-        <v>792.7</v>
+        <v>805.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>888</v>
+        <v>826</v>
       </c>
       <c r="C29" t="n">
-        <v>759</v>
+        <v>851</v>
       </c>
       <c r="D29" t="n">
-        <v>835</v>
+        <v>1002</v>
       </c>
       <c r="E29" t="n">
         <v>799</v>
       </c>
       <c r="F29" t="n">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G29" t="n">
-        <v>783</v>
+        <v>875</v>
       </c>
       <c r="H29" t="n">
-        <v>827</v>
+        <v>843</v>
       </c>
       <c r="I29" t="n">
-        <v>892</v>
+        <v>769</v>
       </c>
       <c r="J29" t="n">
-        <v>883</v>
+        <v>793</v>
       </c>
       <c r="K29" t="n">
-        <v>771</v>
+        <v>863</v>
       </c>
       <c r="L29" t="n">
-        <v>817.3</v>
+        <v>835.5</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>894</v>
+        <v>924</v>
       </c>
       <c r="C30" t="n">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="D30" t="n">
-        <v>750</v>
+        <v>826</v>
       </c>
       <c r="E30" t="n">
-        <v>809</v>
+        <v>833</v>
       </c>
       <c r="F30" t="n">
-        <v>868</v>
+        <v>822</v>
       </c>
       <c r="G30" t="n">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="H30" t="n">
-        <v>749</v>
+        <v>877</v>
       </c>
       <c r="I30" t="n">
-        <v>917</v>
+        <v>796</v>
       </c>
       <c r="J30" t="n">
-        <v>837</v>
+        <v>901</v>
       </c>
       <c r="K30" t="n">
-        <v>796</v>
+        <v>860</v>
       </c>
       <c r="L30" t="n">
-        <v>822.2</v>
+        <v>845.5</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>884</v>
+        <v>907</v>
       </c>
       <c r="C31" t="n">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="D31" t="n">
-        <v>916</v>
+        <v>977</v>
       </c>
       <c r="E31" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F31" t="n">
-        <v>858</v>
+        <v>941</v>
       </c>
       <c r="G31" t="n">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="H31" t="n">
-        <v>789</v>
+        <v>886</v>
       </c>
       <c r="I31" t="n">
-        <v>992</v>
+        <v>878</v>
       </c>
       <c r="J31" t="n">
-        <v>817</v>
+        <v>943</v>
       </c>
       <c r="K31" t="n">
-        <v>1004</v>
+        <v>815</v>
       </c>
       <c r="L31" t="n">
-        <v>888.2</v>
+        <v>896.5</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>909</v>
+        <v>892</v>
       </c>
       <c r="C32" t="n">
-        <v>971</v>
+        <v>1080</v>
       </c>
       <c r="D32" t="n">
-        <v>860</v>
+        <v>886</v>
       </c>
       <c r="E32" t="n">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="F32" t="n">
-        <v>965</v>
+        <v>984</v>
       </c>
       <c r="G32" t="n">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="H32" t="n">
-        <v>915</v>
+        <v>929</v>
       </c>
       <c r="I32" t="n">
-        <v>1010</v>
+        <v>944</v>
       </c>
       <c r="J32" t="n">
-        <v>987</v>
+        <v>935</v>
       </c>
       <c r="K32" t="n">
-        <v>892</v>
+        <v>1020</v>
       </c>
       <c r="L32" t="n">
-        <v>929.7</v>
+        <v>947</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>966</v>
+        <v>786</v>
       </c>
       <c r="C33" t="n">
-        <v>890</v>
+        <v>860</v>
       </c>
       <c r="D33" t="n">
-        <v>861</v>
+        <v>896</v>
       </c>
       <c r="E33" t="n">
-        <v>903</v>
+        <v>857</v>
       </c>
       <c r="F33" t="n">
-        <v>837</v>
+        <v>934</v>
       </c>
       <c r="G33" t="n">
-        <v>876</v>
+        <v>762</v>
       </c>
       <c r="H33" t="n">
-        <v>857</v>
+        <v>916</v>
       </c>
       <c r="I33" t="n">
-        <v>903</v>
+        <v>822</v>
       </c>
       <c r="J33" t="n">
-        <v>745</v>
+        <v>888</v>
       </c>
       <c r="K33" t="n">
-        <v>830</v>
+        <v>812</v>
       </c>
       <c r="L33" t="n">
-        <v>866.8</v>
+        <v>853.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>978</v>
+        <v>845</v>
       </c>
       <c r="C34" t="n">
-        <v>953</v>
+        <v>893</v>
       </c>
       <c r="D34" t="n">
-        <v>915</v>
+        <v>946</v>
       </c>
       <c r="E34" t="n">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F34" t="n">
-        <v>1006</v>
+        <v>867</v>
       </c>
       <c r="G34" t="n">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="H34" t="n">
-        <v>911</v>
+        <v>826</v>
       </c>
       <c r="I34" t="n">
-        <v>935</v>
+        <v>858</v>
       </c>
       <c r="J34" t="n">
-        <v>831</v>
+        <v>863</v>
       </c>
       <c r="K34" t="n">
-        <v>899</v>
+        <v>845</v>
       </c>
       <c r="L34" t="n">
-        <v>918.4</v>
+        <v>870</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>894</v>
+        <v>1042</v>
       </c>
       <c r="C35" t="n">
-        <v>895</v>
+        <v>951</v>
       </c>
       <c r="D35" t="n">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="E35" t="n">
-        <v>955</v>
+        <v>902</v>
       </c>
       <c r="F35" t="n">
-        <v>930</v>
+        <v>899</v>
       </c>
       <c r="G35" t="n">
-        <v>862</v>
+        <v>900</v>
       </c>
       <c r="H35" t="n">
-        <v>798</v>
+        <v>875</v>
       </c>
       <c r="I35" t="n">
-        <v>904</v>
+        <v>833</v>
       </c>
       <c r="J35" t="n">
-        <v>850</v>
+        <v>802</v>
       </c>
       <c r="K35" t="n">
-        <v>855</v>
+        <v>927</v>
       </c>
       <c r="L35" t="n">
-        <v>883.9</v>
+        <v>901.8</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>948</v>
+        <v>965</v>
       </c>
       <c r="C36" t="n">
-        <v>998</v>
+        <v>942</v>
       </c>
       <c r="D36" t="n">
-        <v>1008</v>
+        <v>861</v>
       </c>
       <c r="E36" t="n">
+        <v>931</v>
+      </c>
+      <c r="F36" t="n">
+        <v>851</v>
+      </c>
+      <c r="G36" t="n">
+        <v>867</v>
+      </c>
+      <c r="H36" t="n">
+        <v>943</v>
+      </c>
+      <c r="I36" t="n">
         <v>847</v>
       </c>
-      <c r="F36" t="n">
-        <v>935</v>
-      </c>
-      <c r="G36" t="n">
-        <v>855</v>
-      </c>
-      <c r="H36" t="n">
-        <v>905</v>
-      </c>
-      <c r="I36" t="n">
-        <v>882</v>
-      </c>
       <c r="J36" t="n">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="K36" t="n">
-        <v>862</v>
+        <v>922</v>
       </c>
       <c r="L36" t="n">
-        <v>915.8</v>
+        <v>902.8</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>839</v>
+        <v>878</v>
       </c>
       <c r="C37" t="n">
-        <v>773</v>
+        <v>811</v>
       </c>
       <c r="D37" t="n">
-        <v>872</v>
+        <v>843</v>
       </c>
       <c r="E37" t="n">
-        <v>861</v>
+        <v>809</v>
       </c>
       <c r="F37" t="n">
-        <v>711</v>
+        <v>849</v>
       </c>
       <c r="G37" t="n">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="H37" t="n">
-        <v>850</v>
+        <v>796</v>
       </c>
       <c r="I37" t="n">
-        <v>769</v>
+        <v>940</v>
       </c>
       <c r="J37" t="n">
-        <v>810</v>
+        <v>886</v>
       </c>
       <c r="K37" t="n">
-        <v>857</v>
+        <v>899</v>
       </c>
       <c r="L37" t="n">
-        <v>811.8</v>
+        <v>850.8</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C38" t="n">
-        <v>743</v>
+        <v>800</v>
       </c>
       <c r="D38" t="n">
+        <v>762</v>
+      </c>
+      <c r="E38" t="n">
         <v>814</v>
       </c>
-      <c r="E38" t="n">
-        <v>830</v>
-      </c>
       <c r="F38" t="n">
-        <v>842</v>
+        <v>800</v>
       </c>
       <c r="G38" t="n">
-        <v>785</v>
+        <v>727</v>
       </c>
       <c r="H38" t="n">
-        <v>781</v>
+        <v>874</v>
       </c>
       <c r="I38" t="n">
-        <v>865</v>
+        <v>744</v>
       </c>
       <c r="J38" t="n">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="K38" t="n">
-        <v>737</v>
+        <v>823</v>
       </c>
       <c r="L38" t="n">
-        <v>797.8</v>
+        <v>792.8</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>859</v>
+        <v>813</v>
       </c>
       <c r="C39" t="n">
-        <v>834</v>
+        <v>865</v>
       </c>
       <c r="D39" t="n">
-        <v>884</v>
+        <v>943</v>
       </c>
       <c r="E39" t="n">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="F39" t="n">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="G39" t="n">
-        <v>853</v>
+        <v>756</v>
       </c>
       <c r="H39" t="n">
-        <v>774</v>
+        <v>866</v>
       </c>
       <c r="I39" t="n">
-        <v>828</v>
+        <v>856</v>
       </c>
       <c r="J39" t="n">
-        <v>847</v>
+        <v>946</v>
       </c>
       <c r="K39" t="n">
-        <v>900</v>
+        <v>794</v>
       </c>
       <c r="L39" t="n">
-        <v>841.2</v>
+        <v>848.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>672</v>
+        <v>755</v>
       </c>
       <c r="C40" t="n">
-        <v>765</v>
+        <v>903</v>
       </c>
       <c r="D40" t="n">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="E40" t="n">
-        <v>755</v>
+        <v>790</v>
       </c>
       <c r="F40" t="n">
-        <v>741</v>
+        <v>798</v>
       </c>
       <c r="G40" t="n">
-        <v>752</v>
+        <v>797</v>
       </c>
       <c r="H40" t="n">
-        <v>896</v>
+        <v>797</v>
       </c>
       <c r="I40" t="n">
-        <v>802</v>
+        <v>736</v>
       </c>
       <c r="J40" t="n">
-        <v>824</v>
+        <v>704</v>
       </c>
       <c r="K40" t="n">
-        <v>738</v>
+        <v>833</v>
       </c>
       <c r="L40" t="n">
-        <v>775.7</v>
+        <v>794.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="C41" t="n">
-        <v>699</v>
+        <v>746</v>
       </c>
       <c r="D41" t="n">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="E41" t="n">
-        <v>751</v>
+        <v>714</v>
       </c>
       <c r="F41" t="n">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="G41" t="n">
-        <v>822</v>
+        <v>735</v>
       </c>
       <c r="H41" t="n">
-        <v>674</v>
+        <v>787</v>
       </c>
       <c r="I41" t="n">
-        <v>762</v>
+        <v>841</v>
       </c>
       <c r="J41" t="n">
-        <v>708</v>
+        <v>818</v>
       </c>
       <c r="K41" t="n">
-        <v>791</v>
+        <v>715</v>
       </c>
       <c r="L41" t="n">
-        <v>758.1</v>
+        <v>772.6</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C42" t="n">
-        <v>843</v>
+        <v>866</v>
       </c>
       <c r="D42" t="n">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="E42" t="n">
-        <v>910</v>
+        <v>736</v>
       </c>
       <c r="F42" t="n">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="G42" t="n">
-        <v>771</v>
+        <v>903</v>
       </c>
       <c r="H42" t="n">
-        <v>794</v>
+        <v>761</v>
       </c>
       <c r="I42" t="n">
-        <v>803</v>
+        <v>901</v>
       </c>
       <c r="J42" t="n">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="K42" t="n">
-        <v>768</v>
+        <v>813</v>
       </c>
       <c r="L42" t="n">
-        <v>805.7</v>
+        <v>820.4</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="C43" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="D43" t="n">
-        <v>845</v>
+        <v>758</v>
       </c>
       <c r="E43" t="n">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="F43" t="n">
-        <v>836</v>
+        <v>756</v>
       </c>
       <c r="G43" t="n">
-        <v>889</v>
+        <v>797</v>
       </c>
       <c r="H43" t="n">
-        <v>892</v>
+        <v>787</v>
       </c>
       <c r="I43" t="n">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="J43" t="n">
-        <v>740</v>
+        <v>822</v>
       </c>
       <c r="K43" t="n">
-        <v>877</v>
+        <v>899</v>
       </c>
       <c r="L43" t="n">
-        <v>828.7</v>
+        <v>803.3</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>756</v>
+        <v>685</v>
       </c>
       <c r="C44" t="n">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="D44" t="n">
-        <v>772</v>
+        <v>668</v>
       </c>
       <c r="E44" t="n">
-        <v>746</v>
+        <v>870</v>
       </c>
       <c r="F44" t="n">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="G44" t="n">
-        <v>692</v>
+        <v>718</v>
       </c>
       <c r="H44" t="n">
-        <v>757</v>
+        <v>810</v>
       </c>
       <c r="I44" t="n">
-        <v>890</v>
+        <v>749</v>
       </c>
       <c r="J44" t="n">
-        <v>712</v>
+        <v>741</v>
       </c>
       <c r="K44" t="n">
-        <v>709</v>
+        <v>745</v>
       </c>
       <c r="L44" t="n">
-        <v>755.2</v>
+        <v>750.5</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>946</v>
+        <v>1045</v>
       </c>
       <c r="C45" t="n">
-        <v>963</v>
+        <v>897</v>
       </c>
       <c r="D45" t="n">
-        <v>980</v>
+        <v>847</v>
       </c>
       <c r="E45" t="n">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="F45" t="n">
-        <v>1020</v>
+        <v>962</v>
       </c>
       <c r="G45" t="n">
-        <v>1103</v>
+        <v>901</v>
       </c>
       <c r="H45" t="n">
-        <v>979</v>
+        <v>1010</v>
       </c>
       <c r="I45" t="n">
-        <v>1009</v>
+        <v>932</v>
       </c>
       <c r="J45" t="n">
-        <v>867</v>
+        <v>997</v>
       </c>
       <c r="K45" t="n">
-        <v>901</v>
+        <v>978</v>
       </c>
       <c r="L45" t="n">
-        <v>965</v>
+        <v>948.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>812</v>
+        <v>830</v>
       </c>
       <c r="C46" t="n">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D46" t="n">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="E46" t="n">
-        <v>780</v>
+        <v>934</v>
       </c>
       <c r="F46" t="n">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="G46" t="n">
-        <v>813</v>
+        <v>868</v>
       </c>
       <c r="H46" t="n">
-        <v>811</v>
+        <v>775</v>
       </c>
       <c r="I46" t="n">
-        <v>747</v>
+        <v>815</v>
       </c>
       <c r="J46" t="n">
-        <v>898</v>
+        <v>843</v>
       </c>
       <c r="K46" t="n">
-        <v>934</v>
+        <v>857</v>
       </c>
       <c r="L46" t="n">
-        <v>837</v>
+        <v>849.9</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>841</v>
+        <v>908</v>
       </c>
       <c r="C47" t="n">
-        <v>869</v>
+        <v>905</v>
       </c>
       <c r="D47" t="n">
+        <v>918</v>
+      </c>
+      <c r="E47" t="n">
+        <v>887</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1028</v>
+      </c>
+      <c r="G47" t="n">
         <v>898</v>
       </c>
-      <c r="E47" t="n">
-        <v>828</v>
-      </c>
-      <c r="F47" t="n">
-        <v>809</v>
-      </c>
-      <c r="G47" t="n">
-        <v>893</v>
-      </c>
       <c r="H47" t="n">
-        <v>932</v>
+        <v>895</v>
       </c>
       <c r="I47" t="n">
-        <v>1077</v>
+        <v>1063</v>
       </c>
       <c r="J47" t="n">
-        <v>800</v>
+        <v>931</v>
       </c>
       <c r="K47" t="n">
-        <v>933</v>
+        <v>844</v>
       </c>
       <c r="L47" t="n">
-        <v>888</v>
+        <v>927.7</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>741</v>
+        <v>826</v>
       </c>
       <c r="C48" t="n">
+        <v>787</v>
+      </c>
+      <c r="D48" t="n">
+        <v>673</v>
+      </c>
+      <c r="E48" t="n">
+        <v>731</v>
+      </c>
+      <c r="F48" t="n">
+        <v>662</v>
+      </c>
+      <c r="G48" t="n">
+        <v>775</v>
+      </c>
+      <c r="H48" t="n">
+        <v>671</v>
+      </c>
+      <c r="I48" t="n">
+        <v>805</v>
+      </c>
+      <c r="J48" t="n">
+        <v>750</v>
+      </c>
+      <c r="K48" t="n">
         <v>747</v>
       </c>
-      <c r="D48" t="n">
-        <v>784</v>
-      </c>
-      <c r="E48" t="n">
-        <v>767</v>
-      </c>
-      <c r="F48" t="n">
-        <v>770</v>
-      </c>
-      <c r="G48" t="n">
-        <v>753</v>
-      </c>
-      <c r="H48" t="n">
-        <v>678</v>
-      </c>
-      <c r="I48" t="n">
-        <v>691</v>
-      </c>
-      <c r="J48" t="n">
-        <v>701</v>
-      </c>
-      <c r="K48" t="n">
-        <v>647</v>
-      </c>
       <c r="L48" t="n">
-        <v>727.9</v>
+        <v>742.7</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="C49" t="n">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D49" t="n">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="E49" t="n">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="F49" t="n">
-        <v>734</v>
+        <v>870</v>
       </c>
       <c r="G49" t="n">
-        <v>824</v>
+        <v>730</v>
       </c>
       <c r="H49" t="n">
+        <v>845</v>
+      </c>
+      <c r="I49" t="n">
+        <v>800</v>
+      </c>
+      <c r="J49" t="n">
+        <v>753</v>
+      </c>
+      <c r="K49" t="n">
         <v>779</v>
       </c>
-      <c r="I49" t="n">
-        <v>838</v>
-      </c>
-      <c r="J49" t="n">
-        <v>784</v>
-      </c>
-      <c r="K49" t="n">
-        <v>858</v>
-      </c>
       <c r="L49" t="n">
-        <v>797.4</v>
+        <v>796.6</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>803</v>
+        <v>832</v>
       </c>
       <c r="C50" t="n">
-        <v>745</v>
+        <v>855</v>
       </c>
       <c r="D50" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E50" t="n">
-        <v>853</v>
+        <v>804</v>
       </c>
       <c r="F50" t="n">
-        <v>835</v>
+        <v>783</v>
       </c>
       <c r="G50" t="n">
-        <v>819</v>
+        <v>890</v>
       </c>
       <c r="H50" t="n">
-        <v>809</v>
+        <v>891</v>
       </c>
       <c r="I50" t="n">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="J50" t="n">
+        <v>875</v>
+      </c>
+      <c r="K50" t="n">
         <v>815</v>
       </c>
-      <c r="K50" t="n">
-        <v>806</v>
-      </c>
       <c r="L50" t="n">
-        <v>825.7</v>
+        <v>851.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C51" t="n">
-        <v>811</v>
+        <v>895</v>
       </c>
       <c r="D51" t="n">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="E51" t="n">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="F51" t="n">
-        <v>770</v>
+        <v>918</v>
       </c>
       <c r="G51" t="n">
-        <v>889</v>
+        <v>915</v>
       </c>
       <c r="H51" t="n">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I51" t="n">
-        <v>886</v>
+        <v>821</v>
       </c>
       <c r="J51" t="n">
-        <v>852</v>
+        <v>890</v>
       </c>
       <c r="K51" t="n">
-        <v>809</v>
+        <v>924</v>
       </c>
       <c r="L51" t="n">
-        <v>837.6</v>
+        <v>873.3</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>844.74</v>
+        <v>851.4400000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>837.38</v>
+        <v>857.9</v>
       </c>
       <c r="D52" t="n">
-        <v>852.72</v>
+        <v>849.88</v>
       </c>
       <c r="E52" t="n">
-        <v>854.78</v>
+        <v>853.36</v>
       </c>
       <c r="F52" t="n">
-        <v>836.22</v>
+        <v>847.5599999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>850.48</v>
+        <v>845.4</v>
       </c>
       <c r="H52" t="n">
-        <v>836.9400000000001</v>
+        <v>847.9</v>
       </c>
       <c r="I52" t="n">
-        <v>878.76</v>
+        <v>863</v>
       </c>
       <c r="J52" t="n">
-        <v>838.08</v>
+        <v>853.36</v>
       </c>
       <c r="K52" t="n">
-        <v>843.2</v>
+        <v>859.88</v>
       </c>
       <c r="L52" t="n">
-        <v>847.3299999999998</v>
+        <v>852.9680000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.385218620300293</v>
+        <v>7.564199209213257</v>
       </c>
       <c r="C2" t="n">
-        <v>8.082472562789917</v>
+        <v>7.713842630386353</v>
       </c>
       <c r="D2" t="n">
-        <v>7.070521831512451</v>
+        <v>9.44094181060791</v>
       </c>
       <c r="E2" t="n">
-        <v>10.15563917160034</v>
+        <v>7.735109090805054</v>
       </c>
       <c r="F2" t="n">
-        <v>8.476927042007446</v>
+        <v>8.361701250076294</v>
       </c>
       <c r="G2" t="n">
-        <v>8.00063419342041</v>
+        <v>8.157668113708496</v>
       </c>
       <c r="H2" t="n">
-        <v>7.686402082443237</v>
+        <v>7.687956094741821</v>
       </c>
       <c r="I2" t="n">
-        <v>7.613843679428101</v>
+        <v>8.246991634368896</v>
       </c>
       <c r="J2" t="n">
-        <v>8.955139875411987</v>
+        <v>8.331855773925781</v>
       </c>
       <c r="K2" t="n">
-        <v>8.014577388763428</v>
+        <v>7.444517135620117</v>
       </c>
       <c r="L2" t="n">
-        <v>8.144137644767762</v>
+        <v>8.068478274345399</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.438096523284912</v>
+        <v>7.512378454208374</v>
       </c>
       <c r="C3" t="n">
-        <v>7.339720726013184</v>
+        <v>8.029534816741943</v>
       </c>
       <c r="D3" t="n">
-        <v>8.016177177429199</v>
+        <v>8.750229835510254</v>
       </c>
       <c r="E3" t="n">
-        <v>8.541267871856689</v>
+        <v>8.175168991088867</v>
       </c>
       <c r="F3" t="n">
-        <v>7.65000581741333</v>
+        <v>7.883924961090088</v>
       </c>
       <c r="G3" t="n">
-        <v>8.904312133789062</v>
+        <v>8.583123922348022</v>
       </c>
       <c r="H3" t="n">
-        <v>8.351698160171509</v>
+        <v>7.988627672195435</v>
       </c>
       <c r="I3" t="n">
-        <v>7.618616342544556</v>
+        <v>7.632537126541138</v>
       </c>
       <c r="J3" t="n">
-        <v>7.345762729644775</v>
+        <v>7.957211256027222</v>
       </c>
       <c r="K3" t="n">
-        <v>7.476454019546509</v>
+        <v>8.984107494354248</v>
       </c>
       <c r="L3" t="n">
-        <v>7.868211150169373</v>
+        <v>8.149684453010559</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.713831901550293</v>
+        <v>8.055967807769775</v>
       </c>
       <c r="C4" t="n">
-        <v>7.733814477920532</v>
+        <v>9.426973342895508</v>
       </c>
       <c r="D4" t="n">
-        <v>7.197742462158203</v>
+        <v>8.515786170959473</v>
       </c>
       <c r="E4" t="n">
-        <v>7.178568124771118</v>
+        <v>8.130776166915894</v>
       </c>
       <c r="F4" t="n">
-        <v>7.42808198928833</v>
+        <v>8.001097202301025</v>
       </c>
       <c r="G4" t="n">
-        <v>7.393207788467407</v>
+        <v>8.023145437240601</v>
       </c>
       <c r="H4" t="n">
-        <v>7.870487928390503</v>
+        <v>7.720813751220703</v>
       </c>
       <c r="I4" t="n">
-        <v>8.113327503204346</v>
+        <v>9.454906463623047</v>
       </c>
       <c r="J4" t="n">
-        <v>8.92825984954834</v>
+        <v>7.850948572158813</v>
       </c>
       <c r="K4" t="n">
-        <v>8.357237100601196</v>
+        <v>8.934721946716309</v>
       </c>
       <c r="L4" t="n">
-        <v>7.791455912590027</v>
+        <v>8.411513686180115</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7.125368356704712</v>
+        <v>8.3656907081604</v>
       </c>
       <c r="C5" t="n">
-        <v>8.405158996582031</v>
+        <v>7.85300874710083</v>
       </c>
       <c r="D5" t="n">
-        <v>7.121674537658691</v>
+        <v>7.492444515228271</v>
       </c>
       <c r="E5" t="n">
-        <v>8.722297191619873</v>
+        <v>7.346766948699951</v>
       </c>
       <c r="F5" t="n">
-        <v>6.724365711212158</v>
+        <v>7.50933837890625</v>
       </c>
       <c r="G5" t="n">
-        <v>7.768223762512207</v>
+        <v>7.879390239715576</v>
       </c>
       <c r="H5" t="n">
-        <v>7.150272846221924</v>
+        <v>7.390152931213379</v>
       </c>
       <c r="I5" t="n">
-        <v>7.569226741790771</v>
+        <v>8.02352237701416</v>
       </c>
       <c r="J5" t="n">
-        <v>7.118349552154541</v>
+        <v>7.303888559341431</v>
       </c>
       <c r="K5" t="n">
-        <v>8.337831497192383</v>
+        <v>7.771663188934326</v>
       </c>
       <c r="L5" t="n">
-        <v>7.60427691936493</v>
+        <v>7.693586659431458</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>7.31192421913147</v>
+        <v>8.457002878189087</v>
       </c>
       <c r="C6" t="n">
-        <v>7.342803716659546</v>
+        <v>8.878145217895508</v>
       </c>
       <c r="D6" t="n">
-        <v>8.597126245498657</v>
+        <v>7.122945070266724</v>
       </c>
       <c r="E6" t="n">
-        <v>7.721912860870361</v>
+        <v>8.12739372253418</v>
       </c>
       <c r="F6" t="n">
-        <v>7.410115957260132</v>
+        <v>7.633639574050903</v>
       </c>
       <c r="G6" t="n">
-        <v>7.284436464309692</v>
+        <v>8.487905502319336</v>
       </c>
       <c r="H6" t="n">
-        <v>7.334798336029053</v>
+        <v>7.589273929595947</v>
       </c>
       <c r="I6" t="n">
-        <v>9.133708715438843</v>
+        <v>7.944861173629761</v>
       </c>
       <c r="J6" t="n">
-        <v>7.132461309432983</v>
+        <v>7.765820026397705</v>
       </c>
       <c r="K6" t="n">
-        <v>8.090985059738159</v>
+        <v>7.291999816894531</v>
       </c>
       <c r="L6" t="n">
-        <v>7.736027288436889</v>
+        <v>7.929898691177368</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.527948379516602</v>
+        <v>8.780644655227661</v>
       </c>
       <c r="C7" t="n">
-        <v>7.593242883682251</v>
+        <v>8.940744400024414</v>
       </c>
       <c r="D7" t="n">
-        <v>7.544382572174072</v>
+        <v>8.135327339172363</v>
       </c>
       <c r="E7" t="n">
-        <v>7.67012357711792</v>
+        <v>8.618564605712891</v>
       </c>
       <c r="F7" t="n">
-        <v>7.840641498565674</v>
+        <v>8.677393674850464</v>
       </c>
       <c r="G7" t="n">
-        <v>7.823643684387207</v>
+        <v>8.425085067749023</v>
       </c>
       <c r="H7" t="n">
-        <v>8.007164716720581</v>
+        <v>7.836376190185547</v>
       </c>
       <c r="I7" t="n">
-        <v>8.86943793296814</v>
+        <v>7.669436454772949</v>
       </c>
       <c r="J7" t="n">
-        <v>7.44362211227417</v>
+        <v>8.259030342102051</v>
       </c>
       <c r="K7" t="n">
-        <v>7.459603309631348</v>
+        <v>8.479909896850586</v>
       </c>
       <c r="L7" t="n">
-        <v>7.777981066703797</v>
+        <v>8.382251262664795</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>7.05115532875061</v>
+        <v>7.680890083312988</v>
       </c>
       <c r="C8" t="n">
-        <v>8.203655958175659</v>
+        <v>7.840012073516846</v>
       </c>
       <c r="D8" t="n">
-        <v>6.778896808624268</v>
+        <v>8.067999601364136</v>
       </c>
       <c r="E8" t="n">
-        <v>8.191704750061035</v>
+        <v>9.121557235717773</v>
       </c>
       <c r="F8" t="n">
-        <v>7.141983985900879</v>
+        <v>7.677006721496582</v>
       </c>
       <c r="G8" t="n">
-        <v>8.489405632019043</v>
+        <v>8.126316070556641</v>
       </c>
       <c r="H8" t="n">
-        <v>7.223198175430298</v>
+        <v>7.919875383377075</v>
       </c>
       <c r="I8" t="n">
-        <v>7.770279884338379</v>
+        <v>9.363677501678467</v>
       </c>
       <c r="J8" t="n">
-        <v>7.498033761978149</v>
+        <v>8.729767084121704</v>
       </c>
       <c r="K8" t="n">
-        <v>9.094847917556763</v>
+        <v>8.17823338508606</v>
       </c>
       <c r="L8" t="n">
-        <v>7.744316220283508</v>
+        <v>8.270533514022826</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>7.751330852508545</v>
+        <v>8.198154926300049</v>
       </c>
       <c r="C9" t="n">
-        <v>7.693060159683228</v>
+        <v>7.49698281288147</v>
       </c>
       <c r="D9" t="n">
-        <v>8.134363174438477</v>
+        <v>8.736763000488281</v>
       </c>
       <c r="E9" t="n">
-        <v>7.724424362182617</v>
+        <v>8.184686660766602</v>
       </c>
       <c r="F9" t="n">
-        <v>9.510747194290161</v>
+        <v>8.719901323318481</v>
       </c>
       <c r="G9" t="n">
-        <v>7.724442958831787</v>
+        <v>9.754125833511353</v>
       </c>
       <c r="H9" t="n">
-        <v>7.731458187103271</v>
+        <v>8.467516899108887</v>
       </c>
       <c r="I9" t="n">
-        <v>7.86008620262146</v>
+        <v>7.521919012069702</v>
       </c>
       <c r="J9" t="n">
-        <v>7.195336580276489</v>
+        <v>8.018134832382202</v>
       </c>
       <c r="K9" t="n">
-        <v>7.623605012893677</v>
+        <v>7.612168312072754</v>
       </c>
       <c r="L9" t="n">
-        <v>7.894885468482971</v>
+        <v>8.271035361289979</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.534350633621216</v>
+        <v>7.164855480194092</v>
       </c>
       <c r="C10" t="n">
-        <v>6.671027421951294</v>
+        <v>7.799394130706787</v>
       </c>
       <c r="D10" t="n">
-        <v>6.493956804275513</v>
+        <v>7.268569231033325</v>
       </c>
       <c r="E10" t="n">
-        <v>6.600207567214966</v>
+        <v>7.459594249725342</v>
       </c>
       <c r="F10" t="n">
-        <v>6.604215860366821</v>
+        <v>6.949435234069824</v>
       </c>
       <c r="G10" t="n">
-        <v>6.64509391784668</v>
+        <v>7.370823860168457</v>
       </c>
       <c r="H10" t="n">
-        <v>6.701449871063232</v>
+        <v>6.739957094192505</v>
       </c>
       <c r="I10" t="n">
-        <v>6.838600397109985</v>
+        <v>6.953870296478271</v>
       </c>
       <c r="J10" t="n">
-        <v>7.094470024108887</v>
+        <v>7.191786289215088</v>
       </c>
       <c r="K10" t="n">
-        <v>6.836740255355835</v>
+        <v>6.830841064453125</v>
       </c>
       <c r="L10" t="n">
-        <v>6.702011275291443</v>
+        <v>7.172912693023681</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.621791124343872</v>
+        <v>7.071130037307739</v>
       </c>
       <c r="C11" t="n">
-        <v>6.920526266098022</v>
+        <v>7.359217166900635</v>
       </c>
       <c r="D11" t="n">
-        <v>6.306110382080078</v>
+        <v>7.224572658538818</v>
       </c>
       <c r="E11" t="n">
-        <v>7.964303731918335</v>
+        <v>7.16324520111084</v>
       </c>
       <c r="F11" t="n">
-        <v>6.168431043624878</v>
+        <v>7.259024143218994</v>
       </c>
       <c r="G11" t="n">
-        <v>7.941836833953857</v>
+        <v>7.217639207839966</v>
       </c>
       <c r="H11" t="n">
-        <v>6.534013748168945</v>
+        <v>7.061978340148926</v>
       </c>
       <c r="I11" t="n">
-        <v>6.217854738235474</v>
+        <v>6.735324859619141</v>
       </c>
       <c r="J11" t="n">
-        <v>6.464185953140259</v>
+        <v>6.959278583526611</v>
       </c>
       <c r="K11" t="n">
-        <v>7.334420442581177</v>
+        <v>7.514333724975586</v>
       </c>
       <c r="L11" t="n">
-        <v>6.84734742641449</v>
+        <v>7.156574392318726</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.092066764831543</v>
+        <v>7.083430051803589</v>
       </c>
       <c r="C12" t="n">
-        <v>7.180313110351562</v>
+        <v>7.764747381210327</v>
       </c>
       <c r="D12" t="n">
-        <v>7.173898458480835</v>
+        <v>8.418540239334106</v>
       </c>
       <c r="E12" t="n">
-        <v>7.312491655349731</v>
+        <v>8.21605658531189</v>
       </c>
       <c r="F12" t="n">
-        <v>6.869626998901367</v>
+        <v>6.846550941467285</v>
       </c>
       <c r="G12" t="n">
-        <v>7.062665939331055</v>
+        <v>7.540788173675537</v>
       </c>
       <c r="H12" t="n">
-        <v>7.096048593521118</v>
+        <v>7.445049047470093</v>
       </c>
       <c r="I12" t="n">
-        <v>7.096055746078491</v>
+        <v>7.981687307357788</v>
       </c>
       <c r="J12" t="n">
-        <v>6.880577325820923</v>
+        <v>7.68838906288147</v>
       </c>
       <c r="K12" t="n">
-        <v>7.38021445274353</v>
+        <v>7.748292684555054</v>
       </c>
       <c r="L12" t="n">
-        <v>7.114395904541015</v>
+        <v>7.673353147506714</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>6.395701885223389</v>
+        <v>8.130770444869995</v>
       </c>
       <c r="C13" t="n">
-        <v>6.810651779174805</v>
+        <v>7.486412525177002</v>
       </c>
       <c r="D13" t="n">
-        <v>7.222638130187988</v>
+        <v>7.35073447227478</v>
       </c>
       <c r="E13" t="n">
-        <v>7.448063373565674</v>
+        <v>7.412127017974854</v>
       </c>
       <c r="F13" t="n">
-        <v>7.445580720901489</v>
+        <v>7.530303478240967</v>
       </c>
       <c r="G13" t="n">
-        <v>6.72837495803833</v>
+        <v>7.881398677825928</v>
       </c>
       <c r="H13" t="n">
-        <v>7.607622146606445</v>
+        <v>9.626471519470215</v>
       </c>
       <c r="I13" t="n">
-        <v>7.015115737915039</v>
+        <v>7.936378717422485</v>
       </c>
       <c r="J13" t="n">
-        <v>7.220646381378174</v>
+        <v>7.268067121505737</v>
       </c>
       <c r="K13" t="n">
-        <v>9.090831756591797</v>
+        <v>7.44812798500061</v>
       </c>
       <c r="L13" t="n">
-        <v>7.298522686958313</v>
+        <v>7.807079195976257</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.294924259185791</v>
+        <v>8.675932884216309</v>
       </c>
       <c r="C14" t="n">
-        <v>7.463482618331909</v>
+        <v>8.453982830047607</v>
       </c>
       <c r="D14" t="n">
-        <v>7.912850618362427</v>
+        <v>8.321843147277832</v>
       </c>
       <c r="E14" t="n">
-        <v>8.27344536781311</v>
+        <v>8.42804741859436</v>
       </c>
       <c r="F14" t="n">
-        <v>7.354755640029907</v>
+        <v>9.111803293228149</v>
       </c>
       <c r="G14" t="n">
-        <v>8.887835264205933</v>
+        <v>8.959189891815186</v>
       </c>
       <c r="H14" t="n">
-        <v>7.87148118019104</v>
+        <v>9.175103187561035</v>
       </c>
       <c r="I14" t="n">
-        <v>9.459899187088013</v>
+        <v>8.105386972427368</v>
       </c>
       <c r="J14" t="n">
-        <v>7.698931932449341</v>
+        <v>8.479914426803589</v>
       </c>
       <c r="K14" t="n">
-        <v>7.927317142486572</v>
+        <v>9.078845739364624</v>
       </c>
       <c r="L14" t="n">
-        <v>8.014492321014405</v>
+        <v>8.679004979133605</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>7.826786518096924</v>
+        <v>8.684890985488892</v>
       </c>
       <c r="C15" t="n">
-        <v>8.785624265670776</v>
+        <v>8.47195029258728</v>
       </c>
       <c r="D15" t="n">
-        <v>8.713274240493774</v>
+        <v>8.882371425628662</v>
       </c>
       <c r="E15" t="n">
-        <v>8.214576482772827</v>
+        <v>8.531266212463379</v>
       </c>
       <c r="F15" t="n">
-        <v>7.558763027191162</v>
+        <v>8.220585823059082</v>
       </c>
       <c r="G15" t="n">
-        <v>7.665495872497559</v>
+        <v>8.426085472106934</v>
       </c>
       <c r="H15" t="n">
-        <v>8.506845712661743</v>
+        <v>8.318829774856567</v>
       </c>
       <c r="I15" t="n">
-        <v>8.100902318954468</v>
+        <v>8.325814485549927</v>
       </c>
       <c r="J15" t="n">
-        <v>8.078918218612671</v>
+        <v>9.163153409957886</v>
       </c>
       <c r="K15" t="n">
-        <v>8.054484605789185</v>
+        <v>8.215624809265137</v>
       </c>
       <c r="L15" t="n">
-        <v>8.150567126274108</v>
+        <v>8.524057269096375</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.045050144195557</v>
+        <v>7.843323945999146</v>
       </c>
       <c r="C16" t="n">
-        <v>6.986198902130127</v>
+        <v>6.856023550033569</v>
       </c>
       <c r="D16" t="n">
-        <v>9.048943281173706</v>
+        <v>7.456985712051392</v>
       </c>
       <c r="E16" t="n">
-        <v>6.976232051849365</v>
+        <v>7.501346349716187</v>
       </c>
       <c r="F16" t="n">
-        <v>7.855978012084961</v>
+        <v>7.710841178894043</v>
       </c>
       <c r="G16" t="n">
-        <v>7.018183469772339</v>
+        <v>7.335841417312622</v>
       </c>
       <c r="H16" t="n">
-        <v>6.742855310440063</v>
+        <v>7.560239315032959</v>
       </c>
       <c r="I16" t="n">
-        <v>6.876493692398071</v>
+        <v>7.159771203994751</v>
       </c>
       <c r="J16" t="n">
-        <v>7.210660696029663</v>
+        <v>7.245527505874634</v>
       </c>
       <c r="K16" t="n">
-        <v>7.131377696990967</v>
+        <v>7.542299270629883</v>
       </c>
       <c r="L16" t="n">
-        <v>7.289197325706482</v>
+        <v>7.421219944953918</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>7.463497400283813</v>
+        <v>7.854373931884766</v>
       </c>
       <c r="C17" t="n">
-        <v>7.093926906585693</v>
+        <v>7.611176013946533</v>
       </c>
       <c r="D17" t="n">
-        <v>8.503879070281982</v>
+        <v>8.002151250839233</v>
       </c>
       <c r="E17" t="n">
-        <v>9.011074781417847</v>
+        <v>8.742759704589844</v>
       </c>
       <c r="F17" t="n">
-        <v>7.398142337799072</v>
+        <v>8.367717742919922</v>
       </c>
       <c r="G17" t="n">
-        <v>8.14176869392395</v>
+        <v>8.001173973083496</v>
       </c>
       <c r="H17" t="n">
-        <v>8.849968910217285</v>
+        <v>8.269972324371338</v>
       </c>
       <c r="I17" t="n">
-        <v>7.436086893081665</v>
+        <v>7.914877653121948</v>
       </c>
       <c r="J17" t="n">
-        <v>7.336824178695679</v>
+        <v>8.726819276809692</v>
       </c>
       <c r="K17" t="n">
-        <v>9.21552586555481</v>
+        <v>8.024125576019287</v>
       </c>
       <c r="L17" t="n">
-        <v>8.04506950378418</v>
+        <v>8.151514744758606</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>10.01849865913391</v>
+        <v>10.17482042312622</v>
       </c>
       <c r="C18" t="n">
-        <v>7.856981515884399</v>
+        <v>9.72671365737915</v>
       </c>
       <c r="D18" t="n">
-        <v>7.919305562973022</v>
+        <v>9.4648597240448</v>
       </c>
       <c r="E18" t="n">
-        <v>9.094430685043335</v>
+        <v>9.050897836685181</v>
       </c>
       <c r="F18" t="n">
-        <v>8.560697793960571</v>
+        <v>9.297798156738281</v>
       </c>
       <c r="G18" t="n">
-        <v>8.300505876541138</v>
+        <v>9.638427257537842</v>
       </c>
       <c r="H18" t="n">
-        <v>8.639984130859375</v>
+        <v>9.260899066925049</v>
       </c>
       <c r="I18" t="n">
-        <v>9.311158657073975</v>
+        <v>9.998091459274292</v>
       </c>
       <c r="J18" t="n">
-        <v>8.171772480010986</v>
+        <v>9.032521724700928</v>
       </c>
       <c r="K18" t="n">
-        <v>8.367134809494019</v>
+        <v>9.643436908721924</v>
       </c>
       <c r="L18" t="n">
-        <v>8.624047017097473</v>
+        <v>9.528846621513367</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.136879205703735</v>
+        <v>6.581708192825317</v>
       </c>
       <c r="C19" t="n">
-        <v>6.524900913238525</v>
+        <v>6.777704954147339</v>
       </c>
       <c r="D19" t="n">
-        <v>6.023653030395508</v>
+        <v>7.183687925338745</v>
       </c>
       <c r="E19" t="n">
-        <v>5.92144775390625</v>
+        <v>6.535826921463013</v>
       </c>
       <c r="F19" t="n">
-        <v>6.188250303268433</v>
+        <v>6.787707805633545</v>
       </c>
       <c r="G19" t="n">
-        <v>6.244622468948364</v>
+        <v>6.685957431793213</v>
       </c>
       <c r="H19" t="n">
-        <v>7.02709174156189</v>
+        <v>7.285932064056396</v>
       </c>
       <c r="I19" t="n">
-        <v>7.485924243927002</v>
+        <v>6.97819709777832</v>
       </c>
       <c r="J19" t="n">
-        <v>5.656079769134521</v>
+        <v>7.031081914901733</v>
       </c>
       <c r="K19" t="n">
-        <v>5.873033761978149</v>
+        <v>7.73479437828064</v>
       </c>
       <c r="L19" t="n">
-        <v>6.308188319206238</v>
+        <v>6.958259868621826</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.426104784011841</v>
+        <v>7.718813896179199</v>
       </c>
       <c r="C20" t="n">
-        <v>6.843069553375244</v>
+        <v>7.8854079246521</v>
       </c>
       <c r="D20" t="n">
-        <v>7.288411378860474</v>
+        <v>8.064943790435791</v>
       </c>
       <c r="E20" t="n">
-        <v>7.436567544937134</v>
+        <v>7.559248208999634</v>
       </c>
       <c r="F20" t="n">
-        <v>8.283975601196289</v>
+        <v>7.22556209564209</v>
       </c>
       <c r="G20" t="n">
-        <v>7.199676513671875</v>
+        <v>8.039508819580078</v>
       </c>
       <c r="H20" t="n">
-        <v>7.500389575958252</v>
+        <v>7.481462955474854</v>
       </c>
       <c r="I20" t="n">
-        <v>7.342860460281372</v>
+        <v>8.016551494598389</v>
       </c>
       <c r="J20" t="n">
-        <v>6.761788129806519</v>
+        <v>7.265474081039429</v>
       </c>
       <c r="K20" t="n">
-        <v>7.331824064254761</v>
+        <v>7.922314405441284</v>
       </c>
       <c r="L20" t="n">
-        <v>7.341466760635376</v>
+        <v>7.717928767204285</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>12.48008942604065</v>
+        <v>10.0381715297699</v>
       </c>
       <c r="C21" t="n">
-        <v>7.379752635955811</v>
+        <v>7.955872535705566</v>
       </c>
       <c r="D21" t="n">
-        <v>8.813554525375366</v>
+        <v>8.618039131164551</v>
       </c>
       <c r="E21" t="n">
-        <v>6.795722723007202</v>
+        <v>9.240422010421753</v>
       </c>
       <c r="F21" t="n">
-        <v>7.387173891067505</v>
+        <v>8.275423765182495</v>
       </c>
       <c r="G21" t="n">
-        <v>6.734350919723511</v>
+        <v>9.330610275268555</v>
       </c>
       <c r="H21" t="n">
-        <v>7.157262325286865</v>
+        <v>8.117376565933228</v>
       </c>
       <c r="I21" t="n">
-        <v>8.796580791473389</v>
+        <v>7.876516342163086</v>
       </c>
       <c r="J21" t="n">
-        <v>7.438059329986572</v>
+        <v>8.162729978561401</v>
       </c>
       <c r="K21" t="n">
-        <v>8.348251104354858</v>
+        <v>7.405714511871338</v>
       </c>
       <c r="L21" t="n">
-        <v>8.133079767227173</v>
+        <v>8.502087664604186</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>7.170213937759399</v>
+        <v>7.839601755142212</v>
       </c>
       <c r="C22" t="n">
-        <v>8.341465950012207</v>
+        <v>7.88003396987915</v>
       </c>
       <c r="D22" t="n">
-        <v>7.483489274978638</v>
+        <v>7.66306209564209</v>
       </c>
       <c r="E22" t="n">
-        <v>6.365280866622925</v>
+        <v>7.761784315109253</v>
       </c>
       <c r="F22" t="n">
-        <v>8.227027177810669</v>
+        <v>8.748737573623657</v>
       </c>
       <c r="G22" t="n">
-        <v>8.612135410308838</v>
+        <v>7.176345586776733</v>
       </c>
       <c r="H22" t="n">
-        <v>8.10088324546814</v>
+        <v>7.415683507919312</v>
       </c>
       <c r="I22" t="n">
-        <v>7.528350830078125</v>
+        <v>7.412207365036011</v>
       </c>
       <c r="J22" t="n">
-        <v>7.356294631958008</v>
+        <v>9.334711790084839</v>
       </c>
       <c r="K22" t="n">
-        <v>6.974720478057861</v>
+        <v>9.623955965042114</v>
       </c>
       <c r="L22" t="n">
-        <v>7.615986180305481</v>
+        <v>8.085612392425537</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.836009740829468</v>
+        <v>9.009550809860229</v>
       </c>
       <c r="C23" t="n">
-        <v>10.03044939041138</v>
+        <v>10.95700788497925</v>
       </c>
       <c r="D23" t="n">
-        <v>8.936765909194946</v>
+        <v>8.46845531463623</v>
       </c>
       <c r="E23" t="n">
-        <v>8.350234270095825</v>
+        <v>8.718791723251343</v>
       </c>
       <c r="F23" t="n">
-        <v>7.944273710250854</v>
+        <v>9.380058288574219</v>
       </c>
       <c r="G23" t="n">
-        <v>8.809555530548096</v>
+        <v>8.484417676925659</v>
       </c>
       <c r="H23" t="n">
-        <v>8.756672620773315</v>
+        <v>10.03490114212036</v>
       </c>
       <c r="I23" t="n">
-        <v>8.211565971374512</v>
+        <v>9.414500713348389</v>
       </c>
       <c r="J23" t="n">
-        <v>8.205099582672119</v>
+        <v>8.728764057159424</v>
       </c>
       <c r="K23" t="n">
-        <v>7.673974752426147</v>
+        <v>8.977632522583008</v>
       </c>
       <c r="L23" t="n">
-        <v>8.575460147857665</v>
+        <v>9.21740801334381</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.882419347763062</v>
+        <v>8.210627794265747</v>
       </c>
       <c r="C24" t="n">
-        <v>6.888458967208862</v>
+        <v>7.597749710083008</v>
       </c>
       <c r="D24" t="n">
-        <v>7.225602626800537</v>
+        <v>7.613173246383667</v>
       </c>
       <c r="E24" t="n">
-        <v>8.412569999694824</v>
+        <v>7.872008085250854</v>
       </c>
       <c r="F24" t="n">
-        <v>6.944302082061768</v>
+        <v>7.851540088653564</v>
       </c>
       <c r="G24" t="n">
-        <v>8.106354951858521</v>
+        <v>8.634555339813232</v>
       </c>
       <c r="H24" t="n">
-        <v>6.696434259414673</v>
+        <v>8.431228399276733</v>
       </c>
       <c r="I24" t="n">
-        <v>6.56829047203064</v>
+        <v>7.608730554580688</v>
       </c>
       <c r="J24" t="n">
-        <v>6.6272873878479</v>
+        <v>7.044169664382935</v>
       </c>
       <c r="K24" t="n">
-        <v>7.096670150756836</v>
+        <v>7.163846492767334</v>
       </c>
       <c r="L24" t="n">
-        <v>7.244839024543762</v>
+        <v>7.802762937545777</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>8.646000623703003</v>
+        <v>9.352652072906494</v>
       </c>
       <c r="C25" t="n">
-        <v>9.561142921447754</v>
+        <v>8.626583337783813</v>
       </c>
       <c r="D25" t="n">
-        <v>8.249516487121582</v>
+        <v>10.3345901966095</v>
       </c>
       <c r="E25" t="n">
-        <v>8.344254970550537</v>
+        <v>9.154695749282837</v>
       </c>
       <c r="F25" t="n">
-        <v>9.902175664901733</v>
+        <v>9.349660873413086</v>
       </c>
       <c r="G25" t="n">
-        <v>8.487929105758667</v>
+        <v>9.06041955947876</v>
       </c>
       <c r="H25" t="n">
-        <v>8.486453056335449</v>
+        <v>8.540257692337036</v>
       </c>
       <c r="I25" t="n">
-        <v>10.27684116363525</v>
+        <v>9.377617597579956</v>
       </c>
       <c r="J25" t="n">
-        <v>8.868930578231812</v>
+        <v>11.07019257545471</v>
       </c>
       <c r="K25" t="n">
-        <v>9.212065458297729</v>
+        <v>9.673351764678955</v>
       </c>
       <c r="L25" t="n">
-        <v>9.003531002998352</v>
+        <v>9.454002141952515</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>7.897949695587158</v>
+        <v>8.605603218078613</v>
       </c>
       <c r="C26" t="n">
-        <v>8.430254936218262</v>
+        <v>8.007162570953369</v>
       </c>
       <c r="D26" t="n">
-        <v>9.336701631546021</v>
+        <v>8.696361541748047</v>
       </c>
       <c r="E26" t="n">
-        <v>8.59312105178833</v>
+        <v>9.35463547706604</v>
       </c>
       <c r="F26" t="n">
-        <v>9.080089330673218</v>
+        <v>8.915302515029907</v>
       </c>
       <c r="G26" t="n">
-        <v>7.796116352081299</v>
+        <v>7.684030771255493</v>
       </c>
       <c r="H26" t="n">
-        <v>7.3348069190979</v>
+        <v>8.675933599472046</v>
       </c>
       <c r="I26" t="n">
-        <v>7.638053894042969</v>
+        <v>7.869524002075195</v>
       </c>
       <c r="J26" t="n">
-        <v>7.558229684829712</v>
+        <v>9.365613698959351</v>
       </c>
       <c r="K26" t="n">
-        <v>8.364212036132812</v>
+        <v>9.022525548934937</v>
       </c>
       <c r="L26" t="n">
-        <v>8.202953553199768</v>
+        <v>8.619669294357299</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>8.564194679260254</v>
+        <v>8.871448755264282</v>
       </c>
       <c r="C27" t="n">
-        <v>8.834511995315552</v>
+        <v>9.116775989532471</v>
       </c>
       <c r="D27" t="n">
-        <v>8.958664417266846</v>
+        <v>9.03846287727356</v>
       </c>
       <c r="E27" t="n">
-        <v>9.183670520782471</v>
+        <v>9.8811194896698</v>
       </c>
       <c r="F27" t="n">
-        <v>9.294845581054688</v>
+        <v>8.44400691986084</v>
       </c>
       <c r="G27" t="n">
-        <v>9.153234720230103</v>
+        <v>9.203023195266724</v>
       </c>
       <c r="H27" t="n">
-        <v>9.514329671859741</v>
+        <v>9.040454864501953</v>
       </c>
       <c r="I27" t="n">
-        <v>10.76216435432434</v>
+        <v>10.27580046653748</v>
       </c>
       <c r="J27" t="n">
-        <v>9.86542010307312</v>
+        <v>9.227537155151367</v>
       </c>
       <c r="K27" t="n">
-        <v>8.115861177444458</v>
+        <v>9.355171680450439</v>
       </c>
       <c r="L27" t="n">
-        <v>9.224689722061157</v>
+        <v>9.245380139350891</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>6.638144493103027</v>
+        <v>7.535335302352905</v>
       </c>
       <c r="C28" t="n">
-        <v>6.925879240036011</v>
+        <v>7.139908790588379</v>
       </c>
       <c r="D28" t="n">
-        <v>6.698445796966553</v>
+        <v>7.999166965484619</v>
       </c>
       <c r="E28" t="n">
-        <v>8.205203056335449</v>
+        <v>7.534883260726929</v>
       </c>
       <c r="F28" t="n">
-        <v>7.161272048950195</v>
+        <v>7.083064079284668</v>
       </c>
       <c r="G28" t="n">
-        <v>7.839046478271484</v>
+        <v>7.096030473709106</v>
       </c>
       <c r="H28" t="n">
-        <v>6.984208822250366</v>
+        <v>7.096014022827148</v>
       </c>
       <c r="I28" t="n">
-        <v>7.867466926574707</v>
+        <v>8.124377727508545</v>
       </c>
       <c r="J28" t="n">
-        <v>7.287434577941895</v>
+        <v>7.699447154998779</v>
       </c>
       <c r="K28" t="n">
-        <v>7.261053323745728</v>
+        <v>7.203733921051025</v>
       </c>
       <c r="L28" t="n">
-        <v>7.286815476417542</v>
+        <v>7.45119616985321</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.211670160293579</v>
+        <v>7.645572662353516</v>
       </c>
       <c r="C29" t="n">
-        <v>7.151263236999512</v>
+        <v>7.813680171966553</v>
       </c>
       <c r="D29" t="n">
-        <v>7.335803985595703</v>
+        <v>8.166297912597656</v>
       </c>
       <c r="E29" t="n">
-        <v>7.245582818984985</v>
+        <v>7.4436354637146</v>
       </c>
       <c r="F29" t="n">
-        <v>7.082470893859863</v>
+        <v>8.353276968002319</v>
       </c>
       <c r="G29" t="n">
-        <v>7.62157678604126</v>
+        <v>7.754324913024902</v>
       </c>
       <c r="H29" t="n">
-        <v>7.136324882507324</v>
+        <v>7.897978782653809</v>
       </c>
       <c r="I29" t="n">
-        <v>7.305904626846313</v>
+        <v>7.747357368469238</v>
       </c>
       <c r="J29" t="n">
-        <v>7.971783638000488</v>
+        <v>7.807662725448608</v>
       </c>
       <c r="K29" t="n">
-        <v>7.682073831558228</v>
+        <v>8.225577354431152</v>
       </c>
       <c r="L29" t="n">
-        <v>7.374445486068725</v>
+        <v>7.885536432266235</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>8.737279891967773</v>
+        <v>7.89892315864563</v>
       </c>
       <c r="C30" t="n">
-        <v>7.125999212265015</v>
+        <v>6.830207824707031</v>
       </c>
       <c r="D30" t="n">
-        <v>7.064130783081055</v>
+        <v>8.03210973739624</v>
       </c>
       <c r="E30" t="n">
-        <v>7.151895999908447</v>
+        <v>7.574269533157349</v>
       </c>
       <c r="F30" t="n">
-        <v>7.233180999755859</v>
+        <v>7.807668924331665</v>
       </c>
       <c r="G30" t="n">
-        <v>7.41373872756958</v>
+        <v>7.414683818817139</v>
       </c>
       <c r="H30" t="n">
-        <v>6.865675210952759</v>
+        <v>7.992192029953003</v>
       </c>
       <c r="I30" t="n">
-        <v>7.816065788269043</v>
+        <v>8.653835535049438</v>
       </c>
       <c r="J30" t="n">
-        <v>7.178831815719604</v>
+        <v>8.478904724121094</v>
       </c>
       <c r="K30" t="n">
-        <v>7.278591394424438</v>
+        <v>7.542305946350098</v>
       </c>
       <c r="L30" t="n">
-        <v>7.386538982391357</v>
+        <v>7.822510123252869</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>6.968872547149658</v>
+        <v>7.921337604522705</v>
       </c>
       <c r="C31" t="n">
-        <v>8.763700246810913</v>
+        <v>7.465456962585449</v>
       </c>
       <c r="D31" t="n">
-        <v>7.248127937316895</v>
+        <v>9.197041988372803</v>
       </c>
       <c r="E31" t="n">
-        <v>7.004768848419189</v>
+        <v>7.422066450119019</v>
       </c>
       <c r="F31" t="n">
-        <v>7.404739618301392</v>
+        <v>7.653999805450439</v>
       </c>
       <c r="G31" t="n">
-        <v>7.560312986373901</v>
+        <v>7.79515528678894</v>
       </c>
       <c r="H31" t="n">
-        <v>7.073602199554443</v>
+        <v>8.900770664215088</v>
       </c>
       <c r="I31" t="n">
-        <v>8.807160377502441</v>
+        <v>8.06652307510376</v>
       </c>
       <c r="J31" t="n">
-        <v>6.865121126174927</v>
+        <v>8.326160430908203</v>
       </c>
       <c r="K31" t="n">
-        <v>8.609598636627197</v>
+        <v>7.682400703430176</v>
       </c>
       <c r="L31" t="n">
-        <v>7.630600452423096</v>
+        <v>8.043091297149658</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.063513278961182</v>
+        <v>7.856969833374023</v>
       </c>
       <c r="C32" t="n">
-        <v>8.578207015991211</v>
+        <v>10.69222712516785</v>
       </c>
       <c r="D32" t="n">
-        <v>8.096426963806152</v>
+        <v>9.458916664123535</v>
       </c>
       <c r="E32" t="n">
-        <v>8.137322425842285</v>
+        <v>8.71326208114624</v>
       </c>
       <c r="F32" t="n">
-        <v>8.577717542648315</v>
+        <v>9.617503881454468</v>
       </c>
       <c r="G32" t="n">
-        <v>8.296357870101929</v>
+        <v>9.033978462219238</v>
       </c>
       <c r="H32" t="n">
-        <v>7.91033411026001</v>
+        <v>9.100296497344971</v>
       </c>
       <c r="I32" t="n">
-        <v>8.780137777328491</v>
+        <v>8.680359125137329</v>
       </c>
       <c r="J32" t="n">
-        <v>9.203558683395386</v>
+        <v>9.506956577301025</v>
       </c>
       <c r="K32" t="n">
-        <v>7.867474317550659</v>
+        <v>9.038962602615356</v>
       </c>
       <c r="L32" t="n">
-        <v>8.351104998588562</v>
+        <v>9.169943284988403</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.557233572006226</v>
+        <v>7.273053169250488</v>
       </c>
       <c r="C33" t="n">
-        <v>7.903379678726196</v>
+        <v>7.953302621841431</v>
       </c>
       <c r="D33" t="n">
-        <v>7.48547101020813</v>
+        <v>7.873487234115601</v>
       </c>
       <c r="E33" t="n">
-        <v>8.345236778259277</v>
+        <v>7.866083383560181</v>
       </c>
       <c r="F33" t="n">
-        <v>7.246535778045654</v>
+        <v>8.81901741027832</v>
       </c>
       <c r="G33" t="n">
-        <v>7.570722103118896</v>
+        <v>7.836596012115479</v>
       </c>
       <c r="H33" t="n">
-        <v>7.133316993713379</v>
+        <v>8.918262243270874</v>
       </c>
       <c r="I33" t="n">
-        <v>7.615601778030396</v>
+        <v>7.864533662796021</v>
       </c>
       <c r="J33" t="n">
-        <v>7.302926063537598</v>
+        <v>9.22602105140686</v>
       </c>
       <c r="K33" t="n">
-        <v>7.487958669662476</v>
+        <v>7.91890549659729</v>
       </c>
       <c r="L33" t="n">
-        <v>7.564838242530823</v>
+        <v>8.154926228523255</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>8.733508825302124</v>
+        <v>8.037071704864502</v>
       </c>
       <c r="C34" t="n">
-        <v>8.055052518844604</v>
+        <v>8.839020013809204</v>
       </c>
       <c r="D34" t="n">
-        <v>7.481059551239014</v>
+        <v>8.839011907577515</v>
       </c>
       <c r="E34" t="n">
-        <v>8.671422481536865</v>
+        <v>8.2999107837677</v>
       </c>
       <c r="F34" t="n">
-        <v>8.187757015228271</v>
+        <v>8.306859493255615</v>
       </c>
       <c r="G34" t="n">
-        <v>7.579683542251587</v>
+        <v>8.47744345664978</v>
       </c>
       <c r="H34" t="n">
-        <v>7.938787221908569</v>
+        <v>7.917879581451416</v>
       </c>
       <c r="I34" t="n">
-        <v>8.278914451599121</v>
+        <v>7.929856538772583</v>
       </c>
       <c r="J34" t="n">
-        <v>7.785189628601074</v>
+        <v>9.29630184173584</v>
       </c>
       <c r="K34" t="n">
-        <v>7.769750356674194</v>
+        <v>7.900441646575928</v>
       </c>
       <c r="L34" t="n">
-        <v>8.048112559318543</v>
+        <v>8.384379696846008</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.329840898513794</v>
+        <v>9.287808895111084</v>
       </c>
       <c r="C35" t="n">
-        <v>7.747776508331299</v>
+        <v>7.822629690170288</v>
       </c>
       <c r="D35" t="n">
-        <v>7.40015435218811</v>
+        <v>8.270976066589355</v>
       </c>
       <c r="E35" t="n">
-        <v>7.565218448638916</v>
+        <v>9.029959678649902</v>
       </c>
       <c r="F35" t="n">
-        <v>8.360724687576294</v>
+        <v>8.472930669784546</v>
       </c>
       <c r="G35" t="n">
-        <v>7.793171405792236</v>
+        <v>7.979254961013794</v>
       </c>
       <c r="H35" t="n">
-        <v>7.400658845901489</v>
+        <v>8.170714616775513</v>
       </c>
       <c r="I35" t="n">
-        <v>7.550770282745361</v>
+        <v>7.753340721130371</v>
       </c>
       <c r="J35" t="n">
-        <v>7.577162742614746</v>
+        <v>8.412103414535522</v>
       </c>
       <c r="K35" t="n">
-        <v>6.763785839080811</v>
+        <v>9.272951126098633</v>
       </c>
       <c r="L35" t="n">
-        <v>7.548926401138305</v>
+        <v>8.447266983985902</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.229034662246704</v>
+        <v>9.351195812225342</v>
       </c>
       <c r="C36" t="n">
-        <v>8.61005973815918</v>
+        <v>8.547272682189941</v>
       </c>
       <c r="D36" t="n">
-        <v>8.694369792938232</v>
+        <v>7.727661371231079</v>
       </c>
       <c r="E36" t="n">
-        <v>7.302393436431885</v>
+        <v>8.332268238067627</v>
       </c>
       <c r="F36" t="n">
-        <v>7.258006572723389</v>
+        <v>7.959207773208618</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36674690246582</v>
+        <v>7.939262628555298</v>
       </c>
       <c r="H36" t="n">
-        <v>7.290913581848145</v>
+        <v>7.937261819839478</v>
       </c>
       <c r="I36" t="n">
-        <v>8.125810146331787</v>
+        <v>7.968697786331177</v>
       </c>
       <c r="J36" t="n">
-        <v>9.549198389053345</v>
+        <v>8.273960590362549</v>
       </c>
       <c r="K36" t="n">
-        <v>7.272980213165283</v>
+        <v>7.575180530548096</v>
       </c>
       <c r="L36" t="n">
-        <v>7.969951343536377</v>
+        <v>8.16119692325592</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>7.362746477127075</v>
+        <v>7.76121997833252</v>
       </c>
       <c r="C37" t="n">
-        <v>6.570276975631714</v>
+        <v>7.254536867141724</v>
       </c>
       <c r="D37" t="n">
-        <v>7.244548320770264</v>
+        <v>7.796113729476929</v>
       </c>
       <c r="E37" t="n">
-        <v>6.639095306396484</v>
+        <v>7.406137228012085</v>
       </c>
       <c r="F37" t="n">
-        <v>6.468040704727173</v>
+        <v>7.295901536941528</v>
       </c>
       <c r="G37" t="n">
-        <v>6.825631380081177</v>
+        <v>8.479426860809326</v>
       </c>
       <c r="H37" t="n">
-        <v>7.044378995895386</v>
+        <v>7.69687557220459</v>
       </c>
       <c r="I37" t="n">
-        <v>6.736719608306885</v>
+        <v>7.851965665817261</v>
       </c>
       <c r="J37" t="n">
-        <v>7.336819887161255</v>
+        <v>7.94474983215332</v>
       </c>
       <c r="K37" t="n">
-        <v>6.81067681312561</v>
+        <v>7.411588668823242</v>
       </c>
       <c r="L37" t="n">
-        <v>6.903893446922302</v>
+        <v>7.689851593971253</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.877456188201904</v>
+        <v>7.30985164642334</v>
       </c>
       <c r="C38" t="n">
-        <v>6.483992576599121</v>
+        <v>7.377683401107788</v>
       </c>
       <c r="D38" t="n">
-        <v>6.686478853225708</v>
+        <v>7.374237775802612</v>
       </c>
       <c r="E38" t="n">
-        <v>6.722356081008911</v>
+        <v>7.575201272964478</v>
       </c>
       <c r="F38" t="n">
-        <v>7.294904232025146</v>
+        <v>7.357240438461304</v>
       </c>
       <c r="G38" t="n">
-        <v>7.36970853805542</v>
+        <v>7.093917608261108</v>
       </c>
       <c r="H38" t="n">
-        <v>7.054038286209106</v>
+        <v>7.49041223526001</v>
       </c>
       <c r="I38" t="n">
-        <v>7.248066425323486</v>
+        <v>7.231591939926147</v>
       </c>
       <c r="J38" t="n">
-        <v>7.037124872207642</v>
+        <v>7.846485614776611</v>
       </c>
       <c r="K38" t="n">
-        <v>6.57529354095459</v>
+        <v>7.076941013336182</v>
       </c>
       <c r="L38" t="n">
-        <v>6.934941959381104</v>
+        <v>7.373356294631958</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>8.632052659988403</v>
+        <v>7.847518920898438</v>
       </c>
       <c r="C39" t="n">
-        <v>7.434110879898071</v>
+        <v>8.295867919921875</v>
       </c>
       <c r="D39" t="n">
-        <v>8.315318822860718</v>
+        <v>8.699298143386841</v>
       </c>
       <c r="E39" t="n">
-        <v>7.665476560592651</v>
+        <v>8.295349836349487</v>
       </c>
       <c r="F39" t="n">
-        <v>7.326845169067383</v>
+        <v>7.975667238235474</v>
       </c>
       <c r="G39" t="n">
-        <v>7.949761867523193</v>
+        <v>7.947253704071045</v>
       </c>
       <c r="H39" t="n">
-        <v>7.544284105300903</v>
+        <v>8.732219934463501</v>
       </c>
       <c r="I39" t="n">
-        <v>8.037527322769165</v>
+        <v>8.506824731826782</v>
       </c>
       <c r="J39" t="n">
-        <v>7.61182689666748</v>
+        <v>8.53476357460022</v>
       </c>
       <c r="K39" t="n">
-        <v>7.610207796096802</v>
+        <v>7.91933274269104</v>
       </c>
       <c r="L39" t="n">
-        <v>7.812741208076477</v>
+        <v>8.27540967464447</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.038693428039551</v>
+        <v>7.552744150161743</v>
       </c>
       <c r="C40" t="n">
-        <v>6.656695365905762</v>
+        <v>8.696322441101074</v>
       </c>
       <c r="D40" t="n">
-        <v>6.810292720794678</v>
+        <v>7.808624267578125</v>
       </c>
       <c r="E40" t="n">
-        <v>6.565355777740479</v>
+        <v>8.160188913345337</v>
       </c>
       <c r="F40" t="n">
-        <v>7.201655149459839</v>
+        <v>7.325812578201294</v>
       </c>
       <c r="G40" t="n">
-        <v>6.937817811965942</v>
+        <v>7.499414682388306</v>
       </c>
       <c r="H40" t="n">
-        <v>8.383622169494629</v>
+        <v>7.78467321395874</v>
       </c>
       <c r="I40" t="n">
-        <v>6.545812845230103</v>
+        <v>7.292891025543213</v>
       </c>
       <c r="J40" t="n">
-        <v>6.882149934768677</v>
+        <v>7.161760091781616</v>
       </c>
       <c r="K40" t="n">
-        <v>7.165270566940308</v>
+        <v>7.278438568115234</v>
       </c>
       <c r="L40" t="n">
-        <v>7.018736577033996</v>
+        <v>7.656086993217468</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>6.769782304763794</v>
+        <v>8.26993727684021</v>
       </c>
       <c r="C41" t="n">
-        <v>6.875454902648926</v>
+        <v>7.283970832824707</v>
       </c>
       <c r="D41" t="n">
-        <v>7.035101413726807</v>
+        <v>7.687896728515625</v>
       </c>
       <c r="E41" t="n">
-        <v>6.904929876327515</v>
+        <v>7.240556955337524</v>
       </c>
       <c r="F41" t="n">
-        <v>7.11438512802124</v>
+        <v>8.140497446060181</v>
       </c>
       <c r="G41" t="n">
-        <v>7.126336574554443</v>
+        <v>7.467468500137329</v>
       </c>
       <c r="H41" t="n">
-        <v>6.667526721954346</v>
+        <v>7.87191915512085</v>
       </c>
       <c r="I41" t="n">
-        <v>7.50440502166748</v>
+        <v>7.476491451263428</v>
       </c>
       <c r="J41" t="n">
-        <v>6.827624320983887</v>
+        <v>8.002143144607544</v>
       </c>
       <c r="K41" t="n">
-        <v>7.181713104248047</v>
+        <v>7.066006183624268</v>
       </c>
       <c r="L41" t="n">
-        <v>7.000725936889649</v>
+        <v>7.650688767433167</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>7.852977275848389</v>
+        <v>7.865451335906982</v>
       </c>
       <c r="C42" t="n">
-        <v>7.520388841629028</v>
+        <v>9.159782886505127</v>
       </c>
       <c r="D42" t="n">
-        <v>7.336436986923218</v>
+        <v>7.72082257270813</v>
       </c>
       <c r="E42" t="n">
-        <v>7.46607518196106</v>
+        <v>7.776173830032349</v>
       </c>
       <c r="F42" t="n">
-        <v>7.401231288909912</v>
+        <v>7.697884798049927</v>
       </c>
       <c r="G42" t="n">
-        <v>7.124477863311768</v>
+        <v>8.910308599472046</v>
       </c>
       <c r="H42" t="n">
-        <v>7.704963207244873</v>
+        <v>7.213647842407227</v>
       </c>
       <c r="I42" t="n">
-        <v>7.29749584197998</v>
+        <v>8.791598796844482</v>
       </c>
       <c r="J42" t="n">
-        <v>7.401752471923828</v>
+        <v>7.895375728607178</v>
       </c>
       <c r="K42" t="n">
-        <v>7.230198860168457</v>
+        <v>8.707897186279297</v>
       </c>
       <c r="L42" t="n">
-        <v>7.433599781990051</v>
+        <v>8.173894357681274</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.069124221801758</v>
+        <v>7.650066375732422</v>
       </c>
       <c r="C43" t="n">
-        <v>7.279114007949829</v>
+        <v>7.207254409790039</v>
       </c>
       <c r="D43" t="n">
-        <v>7.125458002090454</v>
+        <v>7.646124839782715</v>
       </c>
       <c r="E43" t="n">
-        <v>7.188795804977417</v>
+        <v>8.440573930740356</v>
       </c>
       <c r="F43" t="n">
-        <v>7.555373668670654</v>
+        <v>7.790234804153442</v>
       </c>
       <c r="G43" t="n">
-        <v>8.15229058265686</v>
+        <v>7.733874559402466</v>
       </c>
       <c r="H43" t="n">
-        <v>7.854593992233276</v>
+        <v>7.612186908721924</v>
       </c>
       <c r="I43" t="n">
-        <v>7.293540716171265</v>
+        <v>7.625155925750732</v>
       </c>
       <c r="J43" t="n">
-        <v>6.775366067886353</v>
+        <v>8.037117719650269</v>
       </c>
       <c r="K43" t="n">
-        <v>7.680028200149536</v>
+        <v>7.644110202789307</v>
       </c>
       <c r="L43" t="n">
-        <v>7.39736852645874</v>
+        <v>7.738669967651367</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.404665470123291</v>
+        <v>6.967888593673706</v>
       </c>
       <c r="C44" t="n">
-        <v>6.728357315063477</v>
+        <v>6.989284038543701</v>
       </c>
       <c r="D44" t="n">
-        <v>6.260552167892456</v>
+        <v>6.544979333877563</v>
       </c>
       <c r="E44" t="n">
-        <v>6.41665244102478</v>
+        <v>7.846584558486938</v>
       </c>
       <c r="F44" t="n">
-        <v>6.180760622024536</v>
+        <v>6.927471399307251</v>
       </c>
       <c r="G44" t="n">
-        <v>6.117422580718994</v>
+        <v>6.620791912078857</v>
       </c>
       <c r="H44" t="n">
-        <v>6.445607423782349</v>
+        <v>6.847660064697266</v>
       </c>
       <c r="I44" t="n">
-        <v>6.851584672927856</v>
+        <v>7.386262178421021</v>
       </c>
       <c r="J44" t="n">
-        <v>6.55031156539917</v>
+        <v>6.883574247360229</v>
       </c>
       <c r="K44" t="n">
-        <v>6.594723463058472</v>
+        <v>7.024720430374146</v>
       </c>
       <c r="L44" t="n">
-        <v>6.455063772201538</v>
+        <v>7.003921675682068</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.044006586074829</v>
+        <v>10.44484233856201</v>
       </c>
       <c r="C45" t="n">
-        <v>7.632558345794678</v>
+        <v>8.891401052474976</v>
       </c>
       <c r="D45" t="n">
-        <v>8.822533130645752</v>
+        <v>8.588635683059692</v>
       </c>
       <c r="E45" t="n">
-        <v>8.204085350036621</v>
+        <v>9.142687320709229</v>
       </c>
       <c r="F45" t="n">
-        <v>8.985029697418213</v>
+        <v>8.288908004760742</v>
       </c>
       <c r="G45" t="n">
-        <v>9.4225172996521</v>
+        <v>8.926262378692627</v>
       </c>
       <c r="H45" t="n">
-        <v>8.251017332077026</v>
+        <v>9.525712251663208</v>
       </c>
       <c r="I45" t="n">
-        <v>9.02252721786499</v>
+        <v>8.52031135559082</v>
       </c>
       <c r="J45" t="n">
-        <v>7.680032014846802</v>
+        <v>10.01093435287476</v>
       </c>
       <c r="K45" t="n">
-        <v>9.000957012176514</v>
+        <v>10.54204773902893</v>
       </c>
       <c r="L45" t="n">
-        <v>8.506526398658753</v>
+        <v>9.288174247741699</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>6.977830648422241</v>
+        <v>7.497983932495117</v>
       </c>
       <c r="C46" t="n">
-        <v>7.256154298782349</v>
+        <v>7.351342916488647</v>
       </c>
       <c r="D46" t="n">
-        <v>7.180337190628052</v>
+        <v>7.29451584815979</v>
       </c>
       <c r="E46" t="n">
-        <v>7.352417230606079</v>
+        <v>8.466493129730225</v>
       </c>
       <c r="F46" t="n">
-        <v>6.944432020187378</v>
+        <v>7.238158464431763</v>
       </c>
       <c r="G46" t="n">
-        <v>7.204269886016846</v>
+        <v>7.785239458084106</v>
       </c>
       <c r="H46" t="n">
-        <v>6.808913230895996</v>
+        <v>7.653619527816772</v>
       </c>
       <c r="I46" t="n">
-        <v>6.892566204071045</v>
+        <v>7.937864542007446</v>
       </c>
       <c r="J46" t="n">
-        <v>7.556407690048218</v>
+        <v>7.140909671783447</v>
       </c>
       <c r="K46" t="n">
-        <v>7.452543497085571</v>
+        <v>8.182529449462891</v>
       </c>
       <c r="L46" t="n">
-        <v>7.162587189674378</v>
+        <v>7.654865694046021</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.029524326324463</v>
+        <v>8.373654365539551</v>
       </c>
       <c r="C47" t="n">
-        <v>7.815120220184326</v>
+        <v>8.783105373382568</v>
       </c>
       <c r="D47" t="n">
-        <v>7.619592666625977</v>
+        <v>8.927738189697266</v>
       </c>
       <c r="E47" t="n">
-        <v>7.605647802352905</v>
+        <v>8.696374893188477</v>
       </c>
       <c r="F47" t="n">
-        <v>7.786681652069092</v>
+        <v>9.72775936126709</v>
       </c>
       <c r="G47" t="n">
-        <v>7.367240905761719</v>
+        <v>9.544977426528931</v>
       </c>
       <c r="H47" t="n">
-        <v>9.171143770217896</v>
+        <v>10.87381672859192</v>
       </c>
       <c r="I47" t="n">
-        <v>9.702798843383789</v>
+        <v>9.619480848312378</v>
       </c>
       <c r="J47" t="n">
-        <v>7.802119255065918</v>
+        <v>8.515764713287354</v>
       </c>
       <c r="K47" t="n">
-        <v>7.711868524551392</v>
+        <v>8.410547018051147</v>
       </c>
       <c r="L47" t="n">
-        <v>8.061173796653748</v>
+        <v>9.147321891784667</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.314416170120239</v>
+        <v>7.229572296142578</v>
       </c>
       <c r="C48" t="n">
-        <v>6.803645133972168</v>
+        <v>7.3327956199646</v>
       </c>
       <c r="D48" t="n">
-        <v>6.728355646133423</v>
+        <v>6.161317825317383</v>
       </c>
       <c r="E48" t="n">
-        <v>6.430617094039917</v>
+        <v>7.02217960357666</v>
       </c>
       <c r="F48" t="n">
-        <v>6.613143682479858</v>
+        <v>6.929874181747437</v>
       </c>
       <c r="G48" t="n">
-        <v>6.790733814239502</v>
+        <v>8.107839345932007</v>
       </c>
       <c r="H48" t="n">
-        <v>6.427613973617554</v>
+        <v>6.845593214035034</v>
       </c>
       <c r="I48" t="n">
-        <v>6.267050504684448</v>
+        <v>7.040052652359009</v>
       </c>
       <c r="J48" t="n">
-        <v>6.808656692504883</v>
+        <v>7.028114080429077</v>
       </c>
       <c r="K48" t="n">
-        <v>6.263541460037231</v>
+        <v>6.730834484100342</v>
       </c>
       <c r="L48" t="n">
-        <v>6.544777417182923</v>
+        <v>7.042817330360412</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>6.765272855758667</v>
+        <v>7.173209667205811</v>
       </c>
       <c r="C49" t="n">
-        <v>6.740828990936279</v>
+        <v>7.262033462524414</v>
       </c>
       <c r="D49" t="n">
-        <v>6.661035060882568</v>
+        <v>7.509379863739014</v>
       </c>
       <c r="E49" t="n">
-        <v>7.579684019088745</v>
+        <v>7.611592292785645</v>
       </c>
       <c r="F49" t="n">
-        <v>7.253530263900757</v>
+        <v>7.442033052444458</v>
       </c>
       <c r="G49" t="n">
-        <v>6.797718524932861</v>
+        <v>6.846580028533936</v>
       </c>
       <c r="H49" t="n">
-        <v>6.698419094085693</v>
+        <v>7.152760982513428</v>
       </c>
       <c r="I49" t="n">
-        <v>6.816673278808594</v>
+        <v>7.62958836555481</v>
       </c>
       <c r="J49" t="n">
-        <v>6.766249895095825</v>
+        <v>7.172214508056641</v>
       </c>
       <c r="K49" t="n">
-        <v>6.718375682830811</v>
+        <v>7.176697731018066</v>
       </c>
       <c r="L49" t="n">
-        <v>6.87977876663208</v>
+        <v>7.297608995437622</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>7.468467712402344</v>
+        <v>8.013308763504028</v>
       </c>
       <c r="C50" t="n">
-        <v>7.424082040786743</v>
+        <v>8.07691764831543</v>
       </c>
       <c r="D50" t="n">
-        <v>6.956778287887573</v>
+        <v>7.694396734237671</v>
       </c>
       <c r="E50" t="n">
-        <v>7.757622003555298</v>
+        <v>7.585678815841675</v>
       </c>
       <c r="F50" t="n">
-        <v>7.403257608413696</v>
+        <v>8.237040281295776</v>
       </c>
       <c r="G50" t="n">
-        <v>7.628676176071167</v>
+        <v>9.470483541488647</v>
       </c>
       <c r="H50" t="n">
-        <v>7.479522228240967</v>
+        <v>8.086922645568848</v>
       </c>
       <c r="I50" t="n">
-        <v>7.618605136871338</v>
+        <v>9.167184352874756</v>
       </c>
       <c r="J50" t="n">
-        <v>7.76622748374939</v>
+        <v>9.014532089233398</v>
       </c>
       <c r="K50" t="n">
-        <v>7.800631523132324</v>
+        <v>7.640625</v>
       </c>
       <c r="L50" t="n">
-        <v>7.530387020111084</v>
+        <v>8.298708987236022</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.001652956008911</v>
+        <v>7.005140066146851</v>
       </c>
       <c r="C51" t="n">
-        <v>6.615157604217529</v>
+        <v>8.129787445068359</v>
       </c>
       <c r="D51" t="n">
-        <v>7.222590684890747</v>
+        <v>7.488406419754028</v>
       </c>
       <c r="E51" t="n">
-        <v>6.710390329360962</v>
+        <v>7.191760301589966</v>
       </c>
       <c r="F51" t="n">
-        <v>6.04111123085022</v>
+        <v>7.725793600082397</v>
       </c>
       <c r="G51" t="n">
-        <v>7.070974111557007</v>
+        <v>8.709295988082886</v>
       </c>
       <c r="H51" t="n">
-        <v>7.169774293899536</v>
+        <v>7.263770580291748</v>
       </c>
       <c r="I51" t="n">
-        <v>6.584719181060791</v>
+        <v>7.340894222259521</v>
       </c>
       <c r="J51" t="n">
-        <v>6.456081867218018</v>
+        <v>7.702934265136719</v>
       </c>
       <c r="K51" t="n">
-        <v>6.742335557937622</v>
+        <v>7.681514024734497</v>
       </c>
       <c r="L51" t="n">
-        <v>6.761478781700134</v>
+        <v>7.623929691314697</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.574303412437439</v>
+        <v>8.065925855636596</v>
       </c>
       <c r="C52" t="n">
-        <v>7.55387848854065</v>
+        <v>8.07417905330658</v>
       </c>
       <c r="D52" t="n">
-        <v>7.55163001537323</v>
+        <v>8.096819982528686</v>
       </c>
       <c r="E52" t="n">
-        <v>7.660837569236755</v>
+        <v>8.093955354690552</v>
       </c>
       <c r="F52" t="n">
-        <v>7.546679224967956</v>
+        <v>8.018197383880615</v>
       </c>
       <c r="G52" t="n">
-        <v>7.637019562721252</v>
+        <v>8.131537227630615</v>
       </c>
       <c r="H52" t="n">
-        <v>7.538386282920837</v>
+        <v>8.073309688568115</v>
       </c>
       <c r="I52" t="n">
-        <v>7.801585030555725</v>
+        <v>8.080114798545837</v>
       </c>
       <c r="J52" t="n">
-        <v>7.481821994781495</v>
+        <v>8.182425618171692</v>
       </c>
       <c r="K52" t="n">
-        <v>7.626308670043946</v>
+        <v>8.049536919593811</v>
       </c>
       <c r="L52" t="n">
-        <v>7.597245025157929</v>
+        <v>8.086600188255311</v>
       </c>
     </row>
   </sheetData>
